--- a/Documentation/Pumps.xlsx
+++ b/Documentation/Pumps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\admin\Lytrose\repos\Pump-Master-Pro\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BBA169-C374-4AF6-BB39-8A8F992A6FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12BC83A6-DCDD-4FA4-99D0-260B57B685B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{C6B53D70-2F2D-478D-9281-D5E674D4F2A8}"/>
   </bookViews>
@@ -12497,6 +12497,10 @@
       </c>
     </row>
     <row r="13" spans="1:174" x14ac:dyDescent="0.3">
+      <c r="D13" t="str">
+        <f>PumpOG!B2</f>
+        <v>SPSA</v>
+      </c>
       <c r="E13" t="str">
         <f>PumpOG!A2</f>
         <v>2 AF-M</v>
@@ -12535,6 +12539,14 @@
       </c>
     </row>
     <row r="14" spans="1:174" x14ac:dyDescent="0.3">
+      <c r="C14" t="str">
+        <f>PumpOG!B3</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D14" t="str">
+        <f>PumpOG!B3</f>
+        <v>SPSA</v>
+      </c>
       <c r="E14" t="str">
         <f>PumpOG!A3</f>
         <v>3 AF-M</v>
@@ -12549,6 +12561,14 @@
       </c>
     </row>
     <row r="15" spans="1:174" x14ac:dyDescent="0.3">
+      <c r="C15" t="str">
+        <f>PumpOG!B4</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D15" t="str">
+        <f>PumpOG!B4</f>
+        <v>SPSA</v>
+      </c>
       <c r="E15" t="str">
         <f>PumpOG!A4</f>
         <v>4 AF-M</v>
@@ -12563,6 +12583,14 @@
       </c>
     </row>
     <row r="16" spans="1:174" x14ac:dyDescent="0.3">
+      <c r="C16" t="str">
+        <f>PumpOG!B5</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D16" t="str">
+        <f>PumpOG!B5</f>
+        <v>SPSA</v>
+      </c>
       <c r="E16" t="str">
         <f>PumpOG!A5</f>
         <v>6 AF-M</v>
@@ -12576,7 +12604,15 @@
         <v>25.18,0,0,,;25.27,20,20,,;25.1,33,30,,;24.6,47.7,40,,;24.15,58.3,45,,;23.3,72.7,50,,;21.76,93.3,55,,;20,109,56,,;18.25,124,55,,</v>
       </c>
     </row>
-    <row r="17" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C17" t="str">
+        <f>PumpOG!B6</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D17" t="str">
+        <f>PumpOG!B6</f>
+        <v>SPSA</v>
+      </c>
       <c r="E17" t="str">
         <f>PumpOG!A6</f>
         <v>20/18-HDM450G-RUBBER</v>
@@ -12590,7 +12626,15 @@
         <v>14.9,0,0,0.9,;14.9,115.3,40,0.9,;14.8,167.4,50,0.9,;14.7,252.9,60,1.1,;14.3,334.7,70,1.2,;13.9,416.5,75,1.4,;13,576.4,80,1.9,;11.9,728.9,82,2.6,;10.6,911.2,80,3.4,|28,0,0,0,;28.1,171.1,40,0,;28,245.5,50,0,;27.7,342.1,60,0,;27,461.2,70,0,;26.2,569,75,0,;24.6,773.6,80,0,;22.3,1012,82,0,;19.8,1253,80,0,|45.4,0,0,2.6,;45.4,219.4,40,2.6,;45.2,316.1,50,2.7,;44.7,431.4,60,3,;43.7,587.6,70,3.5,;42.6,721.5,75,4.1,;39.8,974.4,80,5.5,;35.9,1298,82,7.7,;32.1,1603,80,10.1,</v>
       </c>
     </row>
-    <row r="18" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C18" t="str">
+        <f>PumpOG!B7</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D18" t="str">
+        <f>PumpOG!B7</f>
+        <v>SPSA</v>
+      </c>
       <c r="E18" t="str">
         <f>PumpOG!A7</f>
         <v>10 AHF-M</v>
@@ -12604,7 +12648,15 @@
         <v>73,0,0,2.5,;73.13,130,40,2.5,;73.1,180,50,3,;72.6,251,60,4,;71.25,362,70,5,;68.5,459,75,6,;62,620,78,8,;54.2,750,75,11,</v>
       </c>
     </row>
-    <row r="19" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C19" t="str">
+        <f>PumpOG!B8</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D19" t="str">
+        <f>PumpOG!B8</f>
+        <v>SPSA</v>
+      </c>
       <c r="E19" t="str">
         <f>PumpOG!A8</f>
         <v>2 AHF-M</v>
@@ -12618,7 +12670,15 @@
         <v>57,0,0,1.6,;56.95,6.1,20,1.6,;56.5,10,30,2.15,;56.1,12.4,35,2.5,;55.6,15,40,2.85,;54.9,18,45,3.34,;54,21.5,50,4,;52.5,27,55,6.6,;50.8,33.25,57,,;48.5,39.8,55,,</v>
       </c>
     </row>
-    <row r="20" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C20" t="str">
+        <f>PumpOG!B9</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D20" t="str">
+        <f>PumpOG!B9</f>
+        <v>SPSA</v>
+      </c>
       <c r="E20" t="str">
         <f>PumpOG!A9</f>
         <v>3 AHF-M</v>
@@ -12632,7 +12692,15 @@
         <v>52.8,0,0,1.1,;53.3,10,20,1.1,;53.5,16.3,30,1.9,;53.5,24.4,40,2.55,;53.3,29,45,2.9,;53,34,50,3.4,;52.5,40.8,55,4,;51.3,50.2,60,4.9,;49,62.3,62,,;46.8,73.1,60,,;44.4,85,55,,</v>
       </c>
     </row>
-    <row r="21" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C21" t="str">
+        <f>PumpOG!B10</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D21" t="str">
+        <f>PumpOG!B10</f>
+        <v>SPSA</v>
+      </c>
       <c r="E21" t="str">
         <f>PumpOG!A10</f>
         <v>4 AHF-M</v>
@@ -12646,7 +12714,15 @@
         <v>68.8,0,0,1.8,;66.8,15.5,20,1.8,;66.05,24.4,30,2.07,;65.5,37.6,40,2.3,;64.8,50,50,2.7,;64,73.5,60,3.6,;63.2,91,64,4.7,;60.8,114.3,66,5.9,;56.9,136.2,64,,</v>
       </c>
     </row>
-    <row r="22" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C22" t="str">
+        <f>PumpOG!B11</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D22" t="str">
+        <f>PumpOG!B11</f>
+        <v>SPSA</v>
+      </c>
       <c r="E22" t="str">
         <f>PumpOG!A11</f>
         <v>6 AHF-M</v>
@@ -12660,7 +12736,15 @@
         <v>60.8,0,0,2.8,;62.05,60,30,2.8,;62.15,90,40,3,;62.15,137.5,50,3.49,;62,171,55,3.85,;61.3,215,60,4.8,;59.9,270.5,62,6,;56,317,63.5,8,;49.2,360,62,,;44.8,376,60,,</v>
       </c>
     </row>
-    <row r="23" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C23" t="str">
+        <f>PumpOG!B12</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D23" t="str">
+        <f>PumpOG!B12</f>
+        <v>SPSA</v>
+      </c>
       <c r="E23" t="str">
         <f>PumpOG!A12</f>
         <v>8 AHF-M</v>
@@ -12674,7 +12758,15 @@
         <v>62.2,0,0,2.5,;62.2,100,40,2.5,;62,140,50,3,;61.3,198,60,4,;60.6,245,65,5,;58.3,335,70,6,;55,415,71.5,8,;49.3,520,70,11,;42.7,620,65,0,</v>
       </c>
     </row>
-    <row r="24" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C24" t="str">
+        <f>PumpOG!B13</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D24" t="str">
+        <f>PumpOG!B13</f>
+        <v>SPSA</v>
+      </c>
       <c r="E24" t="str">
         <f>PumpOG!A13</f>
         <v>AL20MG-460</v>
@@ -12688,7 +12780,15 @@
         <v>14.1,0,0,1.2,;14.1,30.4,50,1.1,;13.3,43.4,60,1.1,;12.9,52.7,65,1.1,;12.5,63.8,69,1.2,;11.6,76.9,71,1.3,;11.6,93.6,71.5,1.6,;10,108.5,71,1.8,;8.7,124.6,68,2.2,|71.8,0,0,6,;70.6,68.8,50,5.9,;68.9,94.8,60,6,;67.2,114.7,65,5.7,;64.8,137.6,69,5.5,;62.3,157.4,73,5.7,;57.7,191.5,71.1,6.7,;53.1,222.5,71,8.2,;49,249.8,69,9.8,;46.5,260.3,68,10.5,|102.1,0,0,8.7,;99.2,81.8,50,8.5,;96.3,113.4,60,8.3,;93.8,135.7,65,7.9,;90.9,161.8,69,7.8,;88,182.9,71,8,;84.7,201.4,72,8.5,;81.4,221.3,72.4,9.1,;78,244.2,72,10.1,;74.3,264,71,11.2,;69.7,290.1,69,13.2,;67.7,300,68,13.9,</v>
       </c>
     </row>
-    <row r="25" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C25" t="str">
+        <f>PumpOG!B14</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D25" t="str">
+        <f>PumpOG!B14</f>
+        <v>SPSA</v>
+      </c>
       <c r="E25" t="str">
         <f>PumpOG!A14</f>
         <v>150 C5-M</v>
@@ -12702,7 +12802,15 @@
         <v>118,0,0,2.5,;124,40,50,2.5,;124.5,59.8,60,2.5,;122.7,80,64,2.6,;120.5,92,66,2.8,;109.4,129.5,70,5.67,;89,169.5,66,10,;82.5,180,0,10,</v>
       </c>
     </row>
-    <row r="26" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C26" t="str">
+        <f>PumpOG!B15</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D26" t="str">
+        <f>PumpOG!B15</f>
+        <v>SPSA</v>
+      </c>
       <c r="E26" t="str">
         <f>PumpOG!A15</f>
         <v>CP150i 285</v>
@@ -12716,7 +12824,15 @@
         <v>59.9,0,0,1.5,;57.4,26.3,30,1.5,;53.9,54.9,53,1.6,;50.8,78.8,65,2.3,;45.6,105.5,74,3.2,;40.3,127.7,75,4.5,;32.9,153.1,74,6.1,;27.8,165.3,68.93,6.8,</v>
       </c>
     </row>
-    <row r="27" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C27" t="str">
+        <f>PumpOG!B16</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D27" t="str">
+        <f>PumpOG!B16</f>
+        <v>SPSA</v>
+      </c>
       <c r="E27" t="str">
         <f>PumpOG!A16</f>
         <v>HH130i</v>
@@ -12730,7 +12846,15 @@
         <v>120.2,0,0,0,;116.5,20.2,38.45,0,;112.3,39.3,57.69,0,;106.7,52.8,58,0,;101,61.9,59,0,;93.7,71.3,54.58,0,;86.3,79.6,48,0,|148.4,0,0,1.5,;144,22,41.41,1.7,;141.7,34.2,52.79,1.7,;132.6,57.1,59.45,2.5,;123.6,71.1,60,3,;115.4,79.4,56,3.7,;106.4,87.9,52,6.5,</v>
       </c>
     </row>
-    <row r="28" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C28" t="str">
+        <f>PumpOG!B17</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D28" t="str">
+        <f>PumpOG!B17</f>
+        <v>SPSA</v>
+      </c>
       <c r="E28" t="str">
         <f>PumpOG!A17</f>
         <v>HL160M</v>
@@ -12744,7 +12868,15 @@
         <v>188.4,0,0,2.2,;186.3,100.6,33,2.2,;184.2,187.4,50,2.3,;176.8,251.6,58,2.4,;168.4,303,61,2.8,;161.1,335.1,62,3.1,;153.7,368.3,61,3.5,;142.1,404.7,59,4,;131.6,440,56,4.5,;120,464.7,52,4.9,;108.4,486.1,47.8,5.4,</v>
       </c>
     </row>
-    <row r="29" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C29" t="str">
+        <f>PumpOG!B18</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D29" t="str">
+        <f>PumpOG!B18</f>
+        <v>SPSA</v>
+      </c>
       <c r="E29" t="str">
         <f>PumpOG!A18</f>
         <v>HL225M</v>
@@ -12758,7 +12890,15 @@
         <v>114.3,0,0,2.4,;112.3,136.7,25,2.3,;107.5,279.1,45,2.4,;101.4,440.5,60,2.5,;95.3,600,68,3.9,;92.6,674.1,70,4.6,;89.8,732.9,71,5.2,;87.1,770.9,70,5.7,;83.7,801.3,68,6,;78.3,831.6,65,6.7,</v>
       </c>
     </row>
-    <row r="30" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C30" t="str">
+        <f>PumpOG!B19</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D30" t="str">
+        <f>PumpOG!B19</f>
+        <v>SPSA</v>
+      </c>
       <c r="E30" t="str">
         <f>PumpOG!A19</f>
         <v>HL250M</v>
@@ -12772,7 +12912,15 @@
         <v>123.4,0,0,2,;121.2,159.7,28,2,;118.2,358.6,50,2,;112.9,540.7,65,2.2,;103.1,700.4,72,2.8,;92.6,843.3,75,3.5,;81.3,958.2,72,4.2,;71.5,1056,68,5,;61.7,1126,62,5.5,;50.4,1182,52,6,;38.4,1224,40.99,6.4,</v>
       </c>
     </row>
-    <row r="31" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C31" t="str">
+        <f>PumpOG!B20</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D31" t="str">
+        <f>PumpOG!B20</f>
+        <v>SPSA</v>
+      </c>
       <c r="E31" t="str">
         <f>PumpOG!A20</f>
         <v xml:space="preserve">PAC H108 </v>
@@ -12786,7 +12934,15 @@
         <v>109.4,0,0,2.8,;96,381.9,60,2.9,;90.8,526.6,70,2.6,;82.5,707.5,75,3.2,;73.8,908.5,79,4.5,;62.5,1166,82,5.9,;52.1,1403,79,7.9,;44.8,1556,74.8,9.1,</v>
       </c>
     </row>
-    <row r="32" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C32" t="str">
+        <f>PumpOG!B21</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D32" t="str">
+        <f>PumpOG!B21</f>
+        <v>SPSA</v>
+      </c>
       <c r="E32" t="str">
         <f>PumpOG!A21</f>
         <v>PAC H108 BACK</v>
@@ -12800,7 +12956,15 @@
         <v>48.8,0,0,0,;43.1,233.2,60,0,;41,321.6,70,0,;38.3,426.1,75,0,;34.2,554.8,79,0,;27.9,771.9,82,0,;22.1,964.8,79,79,;17.9,1085,75,0,;10.4,1266,59,0,|66.2,0,0,0,;58.1,297.5,60,0,;55.4,385.9,70,0,;51,514.6,75,0,;45.4,671.4,79,0,;38.1,900.5,82,0,;30.2,1118,79,0,;26.5,1226,75,0,;17.3,1423,57,0,|86,0,0,2.6,;75.8,353.8,60,2.7,;71.9,462.3,70,2.1,;65.4,619.1,75,2.5,;58.5,783.9,79,3.5,;48.5,1045,82,4.9,;40.4,1262,79,6.5,;35,1391,75,7.6,;27.5,1552,71,8.9,|109.4,0,0,2.8,;96,381.9,60,2.9,;90.8,526.6,70,2.6,;82.5,707.5,75,3.2,;73.8,908.5,79,4.5,;62.5,1166,82,5.9,;52.1,1403,79,7.9,;44.8,1556,74.8,9.1,</v>
       </c>
     </row>
-    <row r="33" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C33" t="str">
+        <f>PumpOG!B22</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D33" t="str">
+        <f>PumpOG!B22</f>
+        <v>SPSA</v>
+      </c>
       <c r="E33" t="str">
         <f>PumpOG!A22</f>
         <v>PAC H64 FSC03</v>
@@ -12814,7 +12978,15 @@
         <v>112.9,0,0,3.3,;104.2,173.9,50,3.4,;100.8,267.8,60,3.4,;97.7,333.9,65,3.7,;86.2,490.4,68,5.1,;79.3,579.1,66,6.9,|153.4,0,0,2.4,;147.5,107.8,35,2.3,;141,194.8,50,2.2,;137.8,300.9,60,2.6,;131.9,391.3,65,3.2,;119.1,532.2,69,4.7,;115,582.6,66,5.9,</v>
       </c>
     </row>
-    <row r="34" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C34" t="str">
+        <f>PumpOG!B23</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D34" t="str">
+        <f>PumpOG!B23</f>
+        <v>SPSA</v>
+      </c>
       <c r="E34" t="str">
         <f>PumpOG!A23</f>
         <v>PAS 150HF 300</v>
@@ -12828,7 +13000,15 @@
         <v>50.1,0,0,4,;44.6,169.2,40,4.2,;43,215.2,50,4.5,;40.3,295.2,63,5.1,;35.8,391,70,6,;29.7,465.7,65,7.1,;22.6,516.9,55,8.1,</v>
       </c>
     </row>
-    <row r="35" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C35" t="str">
+        <f>PumpOG!B24</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D35" t="str">
+        <f>PumpOG!B24</f>
+        <v>SPSA</v>
+      </c>
       <c r="E35" t="str">
         <f>PumpOG!A24</f>
         <v>PAS 150MF 250</v>
@@ -12842,7 +13022,15 @@
         <v>18.3,0,0,0,;14.3,117,60,0,;13.1,160.2,70,0,;10.9,234,77,0,;8.3,307.8,70,0,;4.5,391.4,43.59,0,|24,0,0,0,;18.5,136.5,60,0,;17.1,178.3,70,0,;14.3,263.2,77,0,;10.9,344,70,0,;6.4,427.6,46.57,0,|30.4,0,0,0.5,;23.4,149,60,1.3,;21.6,197.8,70,1.9,;18.1,296.7,77,3.3,;13.3,398.3,70,5.1,;7.9,480.5,46.98,6.7,|37.4,0,0,0.6,;32.2,82.2,37.93,0.5,;28.8,161.6,60,1.5,;26.9,220.1,70,2.1,;22.4,335.7,77,3.9,;14.9,465.2,70,6.4,;7.7,536.2,40.15,8.3,</v>
       </c>
     </row>
-    <row r="36" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C36" t="str">
+        <f>PumpOG!B25</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D36" t="str">
+        <f>PumpOG!B25</f>
+        <v>SPSA</v>
+      </c>
       <c r="E36" t="str">
         <f>PumpOG!A25</f>
         <v>XH150i 560</v>
@@ -12856,7 +13044,15 @@
         <v>184,0,0,2.3,;179.9,27.2,29.98,2.5,;175,54.4,46.67,2.3,;167.9,83.1,60.8,3.1,;161.2,107.1,70,4.2,;154.5,125.6,73,5.4,;148.9,137.2,72.83,6.2,;140.3,149.9,68,7.9,</v>
       </c>
     </row>
-    <row r="37" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C37" t="str">
+        <f>PumpOG!B26</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D37" t="str">
+        <f>PumpOG!B26</f>
+        <v>SPSA</v>
+      </c>
       <c r="E37" t="str">
         <f>PumpOG!A26</f>
         <v>6/4-GR100D-M</v>
@@ -12870,7 +13066,15 @@
         <v>10.2,0,0,0,;9.6,8,30,1.1,;9.2,15.3,45,1.1,;8.8,20.4,50,1.3,;8.5,33.6,58,1.4,;7.6,44,59,1.7,;6.9,54.2,58,2,;5.9,60.4,55,2.3,;3.9,68.2,49.8,2.6,|17.5,0,0,0,;16.8,12,30,0.8,;16.5,17.1,40,1.2,;16.2,26,50,1.5,;16.1,33.6,55,1.5,;15.2,41.4,58,1.7,;14.5,52.6,58.75,2.4,;12.9,64.5,58,3.2,;11.6,71.5,55,3.5,;10.1,76.5,49.8,4.1,|27.5,0,0,0.2,;25.7,15.5,30,0.85,;25.6,28,45,1.4,;24.6,42.3,55,1.9,;24.1,53,58,2.4,;23.1,63.9,58.5,3.1,;21.3,74.4,58,3.7,;19.8,81.9,55,4.3,;18.8,86,49.8,4.9,|39.5,0,0,0.4,;37,18,30,1.15,;36.2,35,45,1.8,;35.5,57,55,2.8,;33.5,74,57.85,3.5,;30.9,85.6,55,4.6,;28.7,92.6,49.8,5.3,|54.5,0,0,0.4,;51,20,30,1.3,;49.9,44,45,2.1,;49,62,50,3.22,;45.8,81.6,54,4.4,;40,98.1,49.8,5.8,</v>
       </c>
     </row>
-    <row r="38" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C38" t="str">
+        <f>PumpOG!B27</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D38" t="str">
+        <f>PumpOG!B27</f>
+        <v>SPSA</v>
+      </c>
       <c r="E38" t="str">
         <f>PumpOG!A27</f>
         <v>10/8-GR200F-M</v>
@@ -12884,7 +13088,15 @@
         <v>13.7,0,0,0,;12.4,75,35,0.5,;11.9,102,45,1.9,;10.6,135.4,50,2.5,;9.3,177,44,3.75,|19.5,0,0,0.6,;17.8,69.7,35,1.7,;17.7,89.4,45,2.1,;16.4,133.8,55,2.5,;15.7,155.6,60,3.5,;14.2,189.4,60,4.4,;12,219.7,54.9,5.6,|26.7,0,0,0.7,;25,60,34,1.1,;23.8,125,55,2,;21.4,190,61.5,4.2,;18.6,230,60,4.8,;15.7,265,54.7,7.5,|35,0,0,0.6,;32.2,62,36,1.1,;31.5,130,55,2.1,;30.6,165.5,60,3.3,;28.4,219.7,63,5.6,;24.6,267.6,60,7.6,;23,283.1,58,8.5,|44.5,0,0,0.6,;41,65,35,1.1,;39.5,140.1,55,2.5,;38.3,182.4,60,3.9,;35,245.8,65,6.7,;28.1,311.3,59,10.1,|54,0,0,0.7,;51.1,75,35,1.2,;49.1,155,54,3.1,;47.5,205,60,4.6,;43.9,263.4,65,7.8,;41.8,284.5,65,8.6,;35.7,335.2,58,11.8,</v>
       </c>
     </row>
-    <row r="39" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C39" t="str">
+        <f>PumpOG!B28</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D39" t="str">
+        <f>PumpOG!B28</f>
+        <v>SPSA</v>
+      </c>
       <c r="E39" t="str">
         <f>PumpOG!A28</f>
         <v>12/10-GR250F-M</v>
@@ -12898,7 +13110,15 @@
         <v>83,0,0,2.6,;80.7,122,36.5,2.6,;79.7,173,50,3.2,;77.7,260,60,3.7,;73,428,70,5.6,;67,618,73,8.4,;60.2,809,69.8,11.9,</v>
       </c>
     </row>
-    <row r="40" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C40" t="str">
+        <f>PumpOG!B29</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D40" t="str">
+        <f>PumpOG!B29</f>
+        <v>SPSA</v>
+      </c>
       <c r="E40" t="str">
         <f>PumpOG!A29</f>
         <v>6/6-GR100E-M</v>
@@ -12912,7 +13132,15 @@
         <v>18.5,0,0,1.6,;15.8,32,42,1.6,;14.8,50,55,2.9,;14.1,70,60,3.4,;9.8,113,44,5.28,;7.4,130,40,6.1,|29.5,0,0,0.5,;26.5,18,30,1.2,;25,42,50,2.3,;24.4,64.2,60,3.5,;22.3,94.5,63,4.8,;18.5,123.2,60,6.2,;15.4,142.7,50,7.3,;11.5,161.2,40,8.5,|41.5,0,0,0.6,;38,24,30,1.1,;34,74,60,3.76,;31.9,114,64.8,5.31,;27.1,146.3,60,7.8,;21.5,174,50,9.9,;16.5,194,40,11,|55.5,0,0,0.7,;49,48,36,2.7,;46.9,94,58,4.57,;42.8,137,66.4,6,;36,171,61,9.65,;23,226,40,14.2,</v>
       </c>
     </row>
-    <row r="41" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C41" t="str">
+        <f>PumpOG!B30</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D41" t="str">
+        <f>PumpOG!B30</f>
+        <v>SPSA</v>
+      </c>
       <c r="E41" t="str">
         <f>PumpOG!A30</f>
         <v>8/6-GR150E-M</v>
@@ -12926,7 +13154,15 @@
         <v>18.4,0,0,3.3,;17.1,16.4,30,3.5,;16.1,29.7,40,3.3,;15.5,39.4,50,3.7,;13.9,69.7,60,3.7,;13.3,82.5,60.2,4.4,;12.2,92.7,60,4.4,;10.1,111.7,50,5.3,;7.4,129.1,40,6.3,|29.6,0,0,0,;26.6,18.4,30,0,;25.5,31.2,40,0,;25,42,50,0,;24.1,63.5,60,0,;22.2,93.2,60.3,0,;18.4,122.4,60,0,;15.1,142.4,50,0,;11.3,160.9,40,0,|41.8,0,0,0,;38,23.1,30,0,;36.8,35.9,40,0,;35.9,48.2,50,0,;34.6,74.3,60,3.7,;31.6,113.2,64.96,5.3,;26.8,146.5,60,0,;21.3,174.2,50,0,;16.6,195.7,40,0,|55.8,0,0,3.7,;50.7,32.8,30,3,;49.3,46.1,40,2.6,;48.4,60.5,50,3.2,;46.4,92.2,60,4.4,;43.3,127,65,6.1,;42.1,135.2,65.2,6.5,;41.1,143.4,65,7.2,;36.3,170.1,60,8.9,;28.6,203.9,50,11.9,;23.2,225.9,39.89,14.2,</v>
       </c>
     </row>
-    <row r="42" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C42" t="str">
+        <f>PumpOG!B31</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D42" t="str">
+        <f>PumpOG!B31</f>
+        <v>SPSA</v>
+      </c>
       <c r="E42" t="str">
         <f>PumpOG!A31</f>
         <v>1.5/1-HD25B-METAL</v>
@@ -12940,7 +13176,15 @@
         <v>93,0,0,3,;90.9,2.8,30,3,;89.8,4.01,40,3.5,;88.5,5.2,45,3.8,;86.4,6.35,50,4,;74.8,10.8,56,8,;57.4,14.4,50,0,;49.7,15.6,45,0,</v>
       </c>
     </row>
-    <row r="43" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C43" t="str">
+        <f>PumpOG!B32</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D43" t="str">
+        <f>PumpOG!B32</f>
+        <v>SPSA</v>
+      </c>
       <c r="E43" t="str">
         <f>PumpOG!A32</f>
         <v>1.5/1-HD25B-RUBBER</v>
@@ -12954,7 +13198,15 @@
         <v>49.2,0,0,2.6,;49,1.7,20,2.6,;48,3,30,3.3,;46.1,4.35,40,4,;44.4,5.3,45,4.8,;42.6,6.2,48,6,;38.9,7.8,50,8,;35,9.1,48,0,;32.4,9.8,45,0,</v>
       </c>
     </row>
-    <row r="44" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C44" t="str">
+        <f>PumpOG!B33</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D44" t="str">
+        <f>PumpOG!B33</f>
+        <v>SPSA</v>
+      </c>
       <c r="E44" t="str">
         <f>PumpOG!A33</f>
         <v>10/8-HD200G-METAL</v>
@@ -12968,7 +13220,15 @@
         <v>14.5,0,0,0.7,;14.3,25.9,30,0.7,;13.7,85,65,0.9,;13.2,115.8,70,1,;11.9,163.9,73.58,2.5,;10.2,203.3,70,4.5,;8.9,229.2,65,5.5,|33,0,0,1.3,;31.9,64.1,45,3.9,;30.8,119.5,65,4.6,;29.1,183.6,75,6.6,;27.3,230.4,77.2,8.6,;24.3,277,75,10,;21.9,313,70,11.2,;19.7,342.5,65,12.7,|57.9,0,0,4.8,;56,112.1,50,4.2,;55.1,147.8,60,5.5,;53.8,197.1,70,6.6,;51.2,255,77,9.2,;48.4,303.1,77.85,11,;42.5,374.5,75,13.4,;38.6,406.6,70,14.3,;33.8,442.3,65,15.8,|90.7,0,0,0.4,;87.6,134.3,50,4.6,;85.7,200.8,65,7.5,;82,284.6,75,10.5,;75.7,375.8,78.8,13.6,;72,416.4,77,14.9,;60.7,506.4,70,17.5,;53.1,550.7,65,19.3,</v>
       </c>
     </row>
-    <row r="45" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C45" t="str">
+        <f>PumpOG!B34</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D45" t="str">
+        <f>PumpOG!B34</f>
+        <v>SPSA</v>
+      </c>
       <c r="E45" t="str">
         <f>PumpOG!A34</f>
         <v>10/8-HD200G-RUBBER</v>
@@ -12982,7 +13242,15 @@
         <v>51.3,0,0,0.8,;50,49.7,35.5,0.9,;51.3,74.5,49,1.1,;50.6,111.8,60,1.3,;49.3,162.5,70,2.2,;46.7,230.8,75,3.6,;43.2,297.1,75.7,5.3,;39,362.3,75,7.2,;33.3,438.9,70,9.6,</v>
       </c>
     </row>
-    <row r="46" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C46" t="str">
+        <f>PumpOG!B35</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D46" t="str">
+        <f>PumpOG!B35</f>
+        <v>SPSA</v>
+      </c>
       <c r="E46" t="str">
         <f>PumpOG!A35</f>
         <v>10/8-HDM200F-METAL</v>
@@ -12996,7 +13264,15 @@
         <v>14.5,0,0,0.7,;14.3,25.9,30,0.7,;13.7,85,65,0.9,;13.2,115.8,70,1,;11.9,163.9,73.58,2.5,;10.2,203.3,70,4.5,;8.9,229.2,65,5.5,|33,0,0,1.3,;31.9,64.1,45,3.9,;30.8,119.5,65,4.6,;29.1,183.6,75,6.6,;27.3,230.4,77.2,8.6,;24.3,277,75,10,;21.9,313,70,11.2,;19.7,342.5,65,12.7,|57.9,0,0,4.8,;56,112.1,50,4.2,;55.1,147.8,60,5.5,;53.8,197.1,70,6.6,;51.2,255,77,9.2,;48.4,303.1,77.85,11,;42.5,374.5,75,13.4,;38.6,406.6,70,14.3,;33.8,442.3,65,15.8,|90.7,0,0,0.4,;87.6,134.3,50,4.6,;85.7,200.8,65,7.5,;82,284.6,75,10.5,;75.7,375.8,78.8,13.6,;72,416.4,77,14.9,;60.7,506.4,70,17.5,;53.1,550.7,65,19.3,</v>
       </c>
     </row>
-    <row r="47" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C47" t="str">
+        <f>PumpOG!B36</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D47" t="str">
+        <f>PumpOG!B36</f>
+        <v>SPSA</v>
+      </c>
       <c r="E47" t="str">
         <f>PumpOG!A36</f>
         <v>10/8-HDM200F-RUBBER</v>
@@ -13010,7 +13286,15 @@
         <v>51.3,0,0,2,;51.4,50,35.5,2,;51.3,77,50,2,;50.9,113,60,2.8,;49.7,162,70,4.4,;46.9,230,75,7,;43.1,298,75.7,10.4,;39,360,75,14.2,;33.5,439.7,70,19.4,</v>
       </c>
     </row>
-    <row r="48" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C48" t="str">
+        <f>PumpOG!B37</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D48" t="str">
+        <f>PumpOG!B37</f>
+        <v>SPSA</v>
+      </c>
       <c r="E48" t="str">
         <f>PumpOG!A37</f>
         <v>10/8-HDP200FF-METAL</v>
@@ -13024,7 +13308,15 @@
         <v>14.5,0,0,0.7,;14.3,25.9,30,0.7,;13.7,85,65,0.9,;13.2,115.8,70,1,;11.9,163.9,73.58,2.6,;10.2,203.3,70,4.5,;8.9,229.2,65,5.5,|33,0,0,1.3,;31.9,64.1,45,3.9,;30.8,119.5,65,4.6,;29.1,183.6,75,6.6,;27.3,230.4,77.2,8.6,;24.3,277,75,10,;21.9,313,70,11.2,;19.7,342.5,65,12.7,|57.9,0,0,4.8,;56,112.1,50,4.2,;55.1,147.8,60,5.5,;53.8,197.1,70,6.6,;51.2,255,77,9.2,;48.4,303.1,77.85,11,;42.5,374.5,75,13.4,;38.6,406.6,70,14.3,;33.8,442.3,65,15.8,|90.7,0,0,0.4,;87.6,134.3,50,4.6,;85.7,200.8,65,7.5,;82,284.6,75,10.5,;75.7,375.8,78.8,13.6,;72,416.4,77,14.9,;60.7,506.4,70,17.5,;53.1,550.7,65,19.3,</v>
       </c>
     </row>
-    <row r="49" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C49" t="str">
+        <f>PumpOG!B38</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D49" t="str">
+        <f>PumpOG!B38</f>
+        <v>SPSA</v>
+      </c>
       <c r="E49" t="str">
         <f>PumpOG!A38</f>
         <v>11/4-HDF100D-METAL</v>
@@ -13038,7 +13330,15 @@
         <v>7,0,0,0.9,;7,14,45,0.9,;7,19.8,55,0.9,;6.7,24.8,60,0.9,;6.4,32.7,64,0.9,;6.1,39.2,66,0.9,;6,44.2,68.1,1,;5.7,46,66,1.1,;5,55.7,64,1.2,|39.9,0,0,0.9,;39.8,31.3,45,2,;39.4,44.6,55,2.5,;39,53.9,60,2.8,;38.3,65.4,64,3.2,;37.1,74.7,66,3.4,;36.6,82.6,67,3.6,;34.9,95.9,68.1,4.1,;33.1,109.6,67,4.5,;31.7,119.3,66,4.7,;29.7,130.8,64,5.1,|70.2,0,0,2.5,;70.5,41.3,45,3.5,;69.8,58.6,55,4.3,;69,70.8,60,4.6,;67.7,85.1,64,5.2,;66.5,96.3,66,5.5,;65.5,104.2,67,5.9,;62,125.7,68.1,6.5,;57.5,152.3,67,7,;55.6,161.3,66,7.4,;52.8,174.3,63,8,</v>
       </c>
     </row>
-    <row r="50" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C50" t="str">
+        <f>PumpOG!B39</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D50" t="str">
+        <f>PumpOG!B39</f>
+        <v>SPSA</v>
+      </c>
       <c r="E50" t="str">
         <f>PumpOG!A39</f>
         <v>12/10-HD250G-METAL</v>
@@ -13052,7 +13352,15 @@
         <v>84.3,0,0,3.1,;84.7,104,40,3.1,;82.9,218,60,4.4,;80.3,303,70,5.2,;78,362,75,6.3,;74.5,430,78,7.6,;67,556,80,11,;60,650,78,14,</v>
       </c>
     </row>
-    <row r="51" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C51" t="str">
+        <f>PumpOG!B40</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D51" t="str">
+        <f>PumpOG!B40</f>
+        <v>SPSA</v>
+      </c>
       <c r="E51" t="str">
         <f>PumpOG!A40</f>
         <v>12/10-HD250G-RUBBER</v>
@@ -13066,7 +13374,15 @@
         <v>44.9,0,0,2,;44.6,80,40,2,;43.9,155,60,3,;42.7,225,70,4,;41.7,272,75,5,;39.3,354,80,6,;36.6,425,81,7,;34,488,80,8,</v>
       </c>
     </row>
-    <row r="52" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C52" t="str">
+        <f>PumpOG!B41</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D52" t="str">
+        <f>PumpOG!B41</f>
+        <v>SPSA</v>
+      </c>
       <c r="E52" t="str">
         <f>PumpOG!A41</f>
         <v>12/10-HDM250F-METAL</v>
@@ -13080,7 +13396,15 @@
         <v>84.3,0,0,3.1,;84.7,104,40,3.1,;82.9,218,60,4.4,;80.3,303,70,5.2,;78,362,75,6.3,;74.5,430,78,7.6,;67,556,80,11,;60,650,78,14,</v>
       </c>
     </row>
-    <row r="53" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C53" t="str">
+        <f>PumpOG!B42</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D53" t="str">
+        <f>PumpOG!B42</f>
+        <v>SPSA</v>
+      </c>
       <c r="E53" t="str">
         <f>PumpOG!A42</f>
         <v>12/10-HDM250F-RUBBER</v>
@@ -13094,7 +13418,15 @@
         <v>44.9,0,0,2,;44.6,80,40,2,;43.9,155,60,3,;42.7,225,70,4,;41.7,272,75,5,;39.3,354,80,6,;36.6,425,81,7,;34,488,80,8,</v>
       </c>
     </row>
-    <row r="54" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C54" t="str">
+        <f>PumpOG!B43</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D54" t="str">
+        <f>PumpOG!B43</f>
+        <v>SPSA</v>
+      </c>
       <c r="E54" t="str">
         <f>PumpOG!A43</f>
         <v>12/10-HDP250FF-METAL</v>
@@ -13108,7 +13440,15 @@
         <v>84.3,0,0,3.1,;84.7,104,40,3.1,;82.9,218,60,4.4,;80.3,303,70,5.2,;78,362,75,6.3,;74.5,430,78,7.6,;67,556,80,11,;60,650,78,14,</v>
       </c>
     </row>
-    <row r="55" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C55" t="str">
+        <f>PumpOG!B44</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D55" t="str">
+        <f>PumpOG!B44</f>
+        <v>SPSA</v>
+      </c>
       <c r="E55" t="str">
         <f>PumpOG!A44</f>
         <v>14/12-HD300GART-METAL</v>
@@ -13122,7 +13462,15 @@
         <v>87.7,0,0,2,;86.6,296.8,60,2.2,;85.6,387.4,68,3,;84.7,450.5,72,3.5,;83.2,543.2,76,5.5,;81.4,631.6,78,6.7,;79.5,709.5,79,8,;76.9,816.8,79.4,10,;73.3,938.9,79,12.3,;69.8,1055,78,13.5,;68,1105,77,13,</v>
       </c>
     </row>
-    <row r="56" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C56" t="str">
+        <f>PumpOG!B45</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D56" t="str">
+        <f>PumpOG!B45</f>
+        <v>SPSA</v>
+      </c>
       <c r="E56" t="str">
         <f>PumpOG!A45</f>
         <v>14/12-HD300G-METAL</v>
@@ -13136,7 +13484,15 @@
         <v>88,0,0,2.5,;88.2,163,40,2.5,;88,225,50,3,;87.2,310,60,4.7,;84.8,460,70,7.3,;80.4,635,75,11,;74.1,810,77,15,;67.1,980,75,19.5,;59.4,1140,70,24.5,</v>
       </c>
     </row>
-    <row r="57" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C57" t="str">
+        <f>PumpOG!B46</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D57" t="str">
+        <f>PumpOG!B46</f>
+        <v>SPSA</v>
+      </c>
       <c r="E57" t="str">
         <f>PumpOG!A46</f>
         <v>14/12-HD300G-RUBBER</v>
@@ -13150,7 +13506,15 @@
         <v>47,0,0,1.7,;46.6,125,40,1.7,;46.2,175,50,1.9,;45.7,226,60,2.3,;44.3,350,70,3.6,;42.7,450,75,4.6,;40.6,565,78,6,;38.8,646,79,7.3,;37.2,705.5,78,8.2,;34.5,800,75,10,;31.8,888.5,70,11.6,</v>
       </c>
     </row>
-    <row r="58" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C58" t="str">
+        <f>PumpOG!B47</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D58" t="str">
+        <f>PumpOG!B47</f>
+        <v>SPSA</v>
+      </c>
       <c r="E58" t="str">
         <f>PumpOG!A47</f>
         <v>14/12-HDM300F-METAL</v>
@@ -13164,7 +13528,15 @@
         <v>88,0,0,2.5,;88.2,163,40,2.5,;88,225,50,3,;87.2,310,60,4.7,;84.8,460,70,7.3,;80.4,635,75,11,;74.1,810,77,15,;67.1,980,75,19.5,;59.4,1140,70,24.5,</v>
       </c>
     </row>
-    <row r="59" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C59" t="str">
+        <f>PumpOG!B48</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D59" t="str">
+        <f>PumpOG!B48</f>
+        <v>SPSA</v>
+      </c>
       <c r="E59" t="str">
         <f>PumpOG!A48</f>
         <v>14/12-HDM300F-RUBBER</v>
@@ -13178,7 +13550,15 @@
         <v>47,0,0,1.7,;46.6,125,40,1.7,;46.2,175,50,1.9,;45.7,226,60,2.3,;44.3,350,70,3.6,;42.7,450,75,4.6,;40.6,565,78,6,;38.8,646,79,7.3,;37.2,705.5,78,8.2,;34.5,800,75,10,;31.8,888.5,70,11.6,</v>
       </c>
     </row>
-    <row r="60" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C60" t="str">
+        <f>PumpOG!B49</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D60" t="str">
+        <f>PumpOG!B49</f>
+        <v>SPSA</v>
+      </c>
       <c r="E60" t="str">
         <f>PumpOG!A49</f>
         <v>14/12-HDP300GP-METAL</v>
@@ -13192,7 +13572,15 @@
         <v>88,0,0,2.5,;88.2,163,40,2.5,;88,225,50,3,;87.2,310,60,4.7,;84.8,460,70,7.3,;80.4,635,75,11,;74.1,810,77,15,;67.1,980,75,19.5,;59.4,1140,70,24.5,</v>
       </c>
     </row>
-    <row r="61" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C61" t="str">
+        <f>PumpOG!B50</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D61" t="str">
+        <f>PumpOG!B50</f>
+        <v>SPSA</v>
+      </c>
       <c r="E61" t="str">
         <f>PumpOG!A50</f>
         <v>15/6-HDF150E-METAL</v>
@@ -13206,7 +13594,15 @@
         <v>11,0,0,1.1,;10.3,37.7,40,1.3,;10.2,53.5,50,1.4,;10.2,63.3,55,1.5,;10,80.3,60,1.6,;9.9,100.4,65,2.2,;9.6,112,67,2.3,;9.3,120.5,67.6,2.4,;9,130.8,67,2.6,;8.4,142.4,65,2.8,;7.4,157.6,60,3,;6.7,165.5,58,3.3,|26.5,0,0,1.1,;25.1,59,40,1.46,;24.8,82.8,50,1.8,;24.6,98.6,55,2.2,;24.3,118.7,60,2.4,;23.8,147.9,65,2.8,;23.2,169.8,67,3.3,;22.3,189.9,67.6,3.5,;21.5,205.7,67,3.8,;20,226.4,65,4,;17.7,250.7,60,4.7,;16.3,261.7,58,5,|39.1,0,0,1.1,;36.9,71.8,40,1.6,;36.5,100.4,50,2.1,;36.2,120.5,55,2.4,;35.9,143.6,60,3.8,;35.1,178.9,65,3.3,;34.2,204.5,67,3.7,;33,227.6,67.6,4,;31.4,251.3,67,4.5,;29.4,275.7,65,5.3,;26.2,306.1,60,5.5,</v>
       </c>
     </row>
-    <row r="62" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C62" t="str">
+        <f>PumpOG!B51</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D62" t="str">
+        <f>PumpOG!B51</f>
+        <v>SPSA</v>
+      </c>
       <c r="E62" t="str">
         <f>PumpOG!A51</f>
         <v>16/14-HD350H-METAL</v>
@@ -13220,7 +13616,15 @@
         <v>62,0,0,4.1,;63.5,220,50,4.1,;63.55,305,60,4.1,;62.8,442,70,4.5,;61.7,558,75,5.3,;59.2,740,80,6.7,;54,980,82,10,;49,1185,80,13.8,</v>
       </c>
     </row>
-    <row r="63" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C63" t="str">
+        <f>PumpOG!B52</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D63" t="str">
+        <f>PumpOG!B52</f>
+        <v>SPSA</v>
+      </c>
       <c r="E63" t="str">
         <f>PumpOG!A52</f>
         <v>16/14-HD350H-RUBBER</v>
@@ -13234,7 +13638,15 @@
         <v>42.3,0,0,3.3,;43.2,190,50,3.3,;43.15,257,60,3.5,;42.5,370,70,4,;41.7,453,75,4.5,;39.8,605,80,5.8,;36.3,800,82,8,;32,1000,80,10.5,</v>
       </c>
     </row>
-    <row r="64" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C64" t="str">
+        <f>PumpOG!B53</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D64" t="str">
+        <f>PumpOG!B53</f>
+        <v>SPSA</v>
+      </c>
       <c r="E64" t="str">
         <f>PumpOG!A53</f>
         <v>16/14-HDM350G-METAL</v>
@@ -13248,7 +13660,15 @@
         <v>62,0,0,4.1,;63.5,220,50,4.1,;63.55,305,60,4.1,;62.8,442,70,4.5,;61.7,558,75,5.3,;59.2,740,80,6.7,;54,980,82,10,;49,1185,80,13.8,</v>
       </c>
     </row>
-    <row r="65" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C65" t="str">
+        <f>PumpOG!B54</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D65" t="str">
+        <f>PumpOG!B54</f>
+        <v>SPSA</v>
+      </c>
       <c r="E65" t="str">
         <f>PumpOG!A54</f>
         <v>16/14-HDM350G-RUBBER</v>
@@ -13262,7 +13682,15 @@
         <v>42.3,0,0,3.3,;43.2,190,50,3.3,;43.15,257,60,3.5,;42.5,370,70,4,;41.7,453,75,4.5,;39.8,605,80,5.8,;36.3,800,82,8,;32,1000,80,10.5,</v>
       </c>
     </row>
-    <row r="66" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C66" t="str">
+        <f>PumpOG!B55</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D66" t="str">
+        <f>PumpOG!B55</f>
+        <v>SPSA</v>
+      </c>
       <c r="E66" t="str">
         <f>PumpOG!A55</f>
         <v xml:space="preserve">2 AHF </v>
@@ -13276,7 +13704,15 @@
         <v>8.4,0,0,2,;8.3,3.9,30,2,;8.3,5.7,40,2,;8.2,6.8,45,2,;8.1,8.2,50,2,;8,9.4,53,2.2,;7.8,10.7,55,2.3,;7.7,12.6,56.6,2.5,;7.3,15.1,55,2.8,;7.3,17.3,53,3.4,|33.8,0,0,2,;33.5,7.8,30,2,;33,11.4,40,2.4,;32.7,13.7,45,2.6,;32.1,16.5,50,3.2,;31.6,18.9,53,3.5,;31.1,21.3,55,3.9,;30.1,25.8,56.6,4.8,;28.8,30.8,55,6,;28.1,33.6,53,6.5,;27.8,35.6,52,51,|57.1,0,0,2,;56.5,10.1,30,2.3,;55.7,14.9,40,2.6,;55.1,17.8,45,3.4,;54.2,21.4,50,4,;53.2,24.4,53,4.5,;52.4,27.4,55,5.3,;50.6,33.3,56.6,6.3,;48.6,40.1,55,7,;47.4,43.9,53,7.4,;47,45.2,52,7.5,</v>
       </c>
     </row>
-    <row r="67" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C67" t="str">
+        <f>PumpOG!B56</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D67" t="str">
+        <f>PumpOG!B56</f>
+        <v>SPSA</v>
+      </c>
       <c r="E67" t="str">
         <f>PumpOG!A56</f>
         <v>2/1.5-HD42B-METAL</v>
@@ -13290,7 +13726,15 @@
         <v>8.2,0,0,1.2,;8.3,2.4,20,1.4,;7.7,4.5,30,1.4,;7,6.1,35,1.4,;4.2,9,36,1.7,|16,0,0,0,;15.2,2.4,20,2.8,;14.6,4.2,30,2.9,;14,5.5,35,1.4,;11.7,9.5,40.2,4.1,;8.8,12,38,5.2,|24.5,0,0,0,;24.2,2.4,20,2.8,;23.8,4,30,2.9,;22.4,6.6,40,3.1,;18.6,11.2,45,4.8,;14.9,14.4,40,7.1,;14.4,14.8,39,7.4,|36,0,0,0,;35.2,2.4,20,2.8,;34.5,4,30,2.9,;33.1,6.5,40,2.9,;31.5,8.8,45,4.1,;26.2,13.6,46.75,6.4,;20.2,17.6,39.8,9.8,|48,0,0,3.2,;47.6,2.7,20,2.8,;46.7,5.6,35,2.8,;43.7,9.8,45,4.3,;36.3,15.9,46,8.4,;26.9,20.8,39.8,12.8,|63.1,0,0,3.2,;62.3,3.3,20,2.8,;61.2,5.8,30,2.6,;58.9,9.3,40,3.6,;55.6,12.4,45,5.7,;47.3,18.1,47.32,10,;34.2,24.1,39.8,17.1,</v>
       </c>
     </row>
-    <row r="68" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C68" t="str">
+        <f>PumpOG!B57</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D68" t="str">
+        <f>PumpOG!B57</f>
+        <v>SPSA</v>
+      </c>
       <c r="E68" t="str">
         <f>PumpOG!A57</f>
         <v>2/1.5-HD42B-RUBBER</v>
@@ -13304,7 +13748,15 @@
         <v>7.2,0,0,0,;7.2,1.1,20,0.8,;7.1,1.9,30,0.9,;7,2.8,40,1,;5.8,5.6,43,1.3,;4.7,7.4,40.55,1.6,|10,0,0,2.2,;10,1.4,20,2.2,;10,2.2,30,2.1,;9.6,3.3,40,2.2,;8.6,5.8,45,2.4,;8.2,6.8,46,2.7,;6.3,9.2,42.5,3.3,|17.4,0,0,2.2,;16.7,1.8,20,2.2,;16.2,2.9,30,2.3,;15.9,4.3,40,2.2,;15.3,5.8,45,2.4,;14.5,7.4,50,2.8,;13.5,9,50.15,3.3,;11.6,10.9,49.98,4.2,|27.5,0,0,0.2,;26.6,2.3,20,2.2,;25.9,3.7,30,2.2,;25.1,5.7,40,2.4,;23.3,8.9,50,3.4,;21.2,11.3,50.95,4.8,;18.5,13.5,49.8,6,|38.2,0,0,2.2,;37,2.7,20,2.1,;34.9,6.8,40,2.6,;33.8,8.5,44,3.2,;29.8,13,50.9,5.7,;26.8,15.5,49.97,8,|44.6,0,0,2.2,;44,2.9,20,2.2,;43.2,4.8,30,2.3,;41.4,7.4,40.5,2.8,;40,9.4,43.8,3.5,;37.4,11.9,51.5,5,;35.2,13.8,50.8,6.5,;32.1,16.5,50,9.3,</v>
       </c>
     </row>
-    <row r="69" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C69" t="str">
+        <f>PumpOG!B58</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D69" t="str">
+        <f>PumpOG!B58</f>
+        <v>SPSA</v>
+      </c>
       <c r="E69" t="str">
         <f>PumpOG!A58</f>
         <v>2/2-CT50B-METAL</v>
@@ -13318,7 +13770,15 @@
         <v>23.5,0,0,0,;22.7,3.4,20,0,;22,6.2,30,0,;21.3,8.2,35,0,;19.7,12.1,40,0,;18.1,15,41,0,;16.2,17.6,39.89,0,</v>
       </c>
     </row>
-    <row r="70" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C70" t="str">
+        <f>PumpOG!B59</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D70" t="str">
+        <f>PumpOG!B59</f>
+        <v>SPSA</v>
+      </c>
       <c r="E70" t="str">
         <f>PumpOG!A59</f>
         <v>2/2-CT50C-METAL</v>
@@ -13332,7 +13792,15 @@
         <v>23.5,0,0,0,;22.7,3.4,20,0,;22,6.2,30,0,;21.3,8.2,35,0,;19.7,12.1,40,0,;18.1,15,41,0,;16.2,17.6,39.89,0,</v>
       </c>
     </row>
-    <row r="71" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C71" t="str">
+        <f>PumpOG!B60</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D71" t="str">
+        <f>PumpOG!B60</f>
+        <v>SPSA</v>
+      </c>
       <c r="E71" t="str">
         <f>PumpOG!A60</f>
         <v>20/18-HDM450G-METAL</v>
@@ -13346,7 +13814,15 @@
         <v>14.6,0,0,0.8,;14.8,114.5,40,0.7,;14.8,159.5,50,0.8,;14.6,224.9,60,0.8,;14.5,319,70,1.2,;14.1,400.8,75,1.3,;13.4,511.2,80,1.6,;12.7,617.6,83,1.9,;11.9,756.6,85,2.3,;10.7,948.9,82.8,2.8,|22.9,0,0,0,;23.2,154.8,40,0,;23.1,203.7,50,0,;22.9,285.1,60,0,;22.5,403.3,70,0,;21.8,505.1,75,0,;20.8,643.6,80,0,;20,773.9,83,0,;18.4,953.2,85,0,;16.7,1185,83,0,|33,0,0,0,;33.4,179.2,40,0,;33.4,240.3,50,0,;33,342.2,60,0,;32.5,484.7,70,0,;31.7,606.9,75,0,;30.3,773.9,80,0,;28.9,928.7,83,0,;26.7,1145,85,0,;24.1,1418,83,0,|45.1,0,0,0,;45.6,207.7,40,0,;45.4,281.1,50,0,;45.1,395.1,60,0,;44.2,566.2,70,0,;43,708.8,75,0,;41.3,900.2,80,0,;39.2,1084,83,0,;36.1,1340,85,0,;32.9,1658,83,0,|73.3,0,0,3.3,;73.8,260.7,40,3.4,;73.5,366.6,50,3.5,;73.1,513.2,60,3.8,;71.9,716.9,70,4.5,;70,904.3,75,5.4,;66.6,1169,80,7,;63.3,1397,83,8.5,;58.3,1723,85,10.4,;52.8,2045,83,11.5,</v>
       </c>
     </row>
-    <row r="72" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C72" t="str">
+        <f>PumpOG!B61</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D72" t="str">
+        <f>PumpOG!B61</f>
+        <v>SPSA</v>
+      </c>
       <c r="E72" t="str">
         <f>PumpOG!A61</f>
         <v>22/8-HDF200F-METAL</v>
@@ -13360,7 +13836,15 @@
         <v>14.8,0,0,1.8,;14.8,64,40,1.8,;14.9,90.5,50,1.8,;14.8,135.2,60,1.8,;14.5,171.4,64,1.8,;14.1,199.2,66,1.8,;13.8,225.8,66.5,1.8,;13.1,262,66,1.9,;12.1,298.2,64,2,|33,0,0,2.4,;33.4,90.5,40,2.6,;33.3,129.2,50,2.7,;32.9,188.3,60,2.9,;32.5,230.6,64,3,;31.9,266.8,66,3.3,;31.2,298.2,67,3.5,;30.2,344.1,67.7,3.7,;29,380.3,67,3.9,;27.7,420.1,66,4.1,;26.1,467.2,64,4.4,|58.3,0,0,4,;58.8,118.3,40,4.4,;58.8,167.8,50,4.5,;58.3,243.9,60,5,;57.4,295.8,64,5.3,;56.4,339.2,66,5.6,;55.5,375.5,67,5.7,;53.3,443.1,67.7,6.2,;50.3,517.9,67,6.5,;48.1,561.4,66,6.8,;45.9,601.2,64,7,</v>
       </c>
     </row>
-    <row r="73" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C73" t="str">
+        <f>PumpOG!B62</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D73" t="str">
+        <f>PumpOG!B62</f>
+        <v>SPSA</v>
+      </c>
       <c r="E73" t="str">
         <f>PumpOG!A62</f>
         <v>3 AHF</v>
@@ -13374,7 +13858,15 @@
         <v>7,0,0,0,;7.1,5.9,30,0,;7.1,8.7,40,0,;7,12.3,50,0,;7,14.4,55,0,;6.9,16.2,58,0,;6.8,18.5,60,0,;6.6,22.6,61.9,0,;6.2,26.2,60,0,;5.9,28.8,58,0,;5.8,30.3,57,0,|28.1,0,0,0,;28.4,12.3,30,0,;28.4,17.5,40,0,;28,24.2,50,0,;27.8,28.8,55,0,;27.4,32.7,58,0,;27.1,36.2,60,0,;26.1,44.5,61.9,0,;24.9,52.8,60,0,;24.3,57.1,58,0,;23.6,61.5,57,0,|52.9,0,0,1.8,;53.6,17,30,1.8,;53.5,24.4,40,2.5,;53,33.9,50,2.5,;52.4,40.1,55,3.4,;51.9,45.2,58,3.8,;51.2,49.9,60,4.3,;49.5,61.3,61.9,4.5,;47.1,72.8,60,5.4,;45.8,78.5,58,6.3,;44.6,82.6,52,6.5,</v>
       </c>
     </row>
-    <row r="74" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C74" t="str">
+        <f>PumpOG!B63</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D74" t="str">
+        <f>PumpOG!B63</f>
+        <v>SPSA</v>
+      </c>
       <c r="E74" t="str">
         <f>PumpOG!A63</f>
         <v>3/2-HD50C-METAL</v>
@@ -13388,7 +13880,15 @@
         <v>88,0,0,3,;88.8,7.2,30,3,;88.5,11.1,40,4,;87.3,16.6,50,6.5,;85.5,20.9,55,8,;82.3,27.2,60,11.5,;79.85,31.1,62,13.5,;75.1,38,63.5,17.6,;69,44.3,62,0,;66,47,60,0,</v>
       </c>
     </row>
-    <row r="75" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C75" t="str">
+        <f>PumpOG!B64</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D75" t="str">
+        <f>PumpOG!B64</f>
+        <v>SPSA</v>
+      </c>
       <c r="E75" t="str">
         <f>PumpOG!A64</f>
         <v>3/2-HD50C-METAL 2V</v>
@@ -13402,7 +13902,15 @@
         <v>17.9,0,0,0.1,;16.8,4.1,30,0.1,;16.4,5.5,35,0.1,;14.9,7.5,40,0.1,;13.4,9.6,41.75,0.1,;11.9,11,40,0.1,|28.5,0,0,0.5,;27.4,4.7,30,0.7,;26.8,6,35,0.6,;25.7,7.9,40,0.7,;24.2,9.8,43,0.7,;22.8,11.2,43.85,0.8,;20.6,13.2,43,0.9,;18.7,14.4,40,0.9,|41.5,0,0,1.5,;40.2,5.2,30,1.7,;39.6,6.6,35,1.8,;38.5,8.6,40,1.9,;37.4,10.3,43,2,;36.6,11.1,44,2,;35.3,12.4,45,2.1,;33.6,13.7,45.45,2.2,;32.1,15,43,2.4,;30,16.2,44,2.5,;28.7,17,43,2.7,;26.6,18.1,40,2.9,|56.8,0,0,2.9,;55.7,5.4,30,3.5,;54.9,7.1,35,3.6,;53.8,9.6,40,3.8,;51.7,11.9,43,4,;50.6,13.1,44,4.2,;48.7,14.6,45,4.3,;44.3,17.8,46,5,;39.8,20.1,45,5.5,;37.4,21.4,44,5.9,;35.7,22.1,43,6,</v>
       </c>
     </row>
-    <row r="76" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C76" t="str">
+        <f>PumpOG!B65</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D76" t="str">
+        <f>PumpOG!B65</f>
+        <v>SPSA</v>
+      </c>
       <c r="E76" t="str">
         <f>PumpOG!A65</f>
         <v>3/2-HD50C-METAL 6V</v>
@@ -13416,7 +13924,15 @@
         <v>56.8,0,0,0,;56,8.5,40,0,;54.9,12.5,50,0,;53.7,15.3,55,0,;51.8,19.5,60,0,;45.3,28.9,64.98,0,;36.5,37.2,58.96,0,|88,0,0,3,;85.7,10.4,40,3.7,;84.1,15.5,50,4.5,;82.4,19.1,55,5.2,;79.9,23.7,60,6.3,;74.8,30.3,65,8.6,;69.2,36.1,67,10.4,;62.5,41.9,65,13.1,;57.2,46,60,15.2,</v>
       </c>
     </row>
-    <row r="77" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C77" t="str">
+        <f>PumpOG!B66</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D77" t="str">
+        <f>PumpOG!B66</f>
+        <v>SPSA</v>
+      </c>
       <c r="E77" t="str">
         <f>PumpOG!A66</f>
         <v>3/2-HD50C-RUBBER</v>
@@ -13430,7 +13946,15 @@
         <v>48,0,0,3.1,;48.4,6.2,40,3.45,;48,8,45,3.5,;47.5,9.5,50,3.4,;46.4,11.9,55,3.5,;44.5,15.25,60,3.8,;40.2,21.2,62,4.25,;36,26.1,60,5,</v>
       </c>
     </row>
-    <row r="78" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C78" t="str">
+        <f>PumpOG!B67</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D78" t="str">
+        <f>PumpOG!B67</f>
+        <v>SPSA</v>
+      </c>
       <c r="E78" t="str">
         <f>PumpOG!A67</f>
         <v>3/2-HHD50D-METAL</v>
@@ -13444,7 +13968,15 @@
         <v>86.9,0,0,1.4,;86.6,8.4,20,1.4,;86.9,14.1,30,1.5,;86.3,22.4,40,2.8,;84.1,28.6,45,4.5,;75.8,38.6,46.8,8.3,;71.7,41.5,47,9.7,</v>
       </c>
     </row>
-    <row r="79" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C79" t="str">
+        <f>PumpOG!B68</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D79" t="str">
+        <f>PumpOG!B68</f>
+        <v>SPSA</v>
+      </c>
       <c r="E79" t="str">
         <f>PumpOG!A68</f>
         <v>4 AHF</v>
@@ -13458,7 +13990,15 @@
         <v>7,0,0,0.9,;7,14,45,0.9,;7,19.8,55,0.9,;6.7,24.8,60,0.9,;6.4,32.7,64,0.9,;6.1,39.2,66,0.9,;6,44.2,68.1,1,;5.7,46,66,1.1,;5,55.7,64,1.2,|39.9,0,0,0.9,;39.8,31.3,45,2,;39.4,44.6,55,2.5,;39,53.9,60,2.8,;38.3,65.4,64,3.2,;37.1,74.7,66,3.4,;36.6,82.6,67,3.6,;34.9,95.9,68.1,4.1,;33.1,109.6,67,4.5,;31.7,119.3,66,4.7,;29.7,130.8,64,5.1,|70.2,0,0,2.5,;70.5,41.3,45,3.5,;69.8,58.6,55,4.3,;69,70.8,60,4.6,;67.7,85.1,64,5.2,;66.5,96.3,66,5.5,;65.5,104.2,67,5.9,;62,125.7,68.1,6.5,;57.5,152.3,67,7,;55.6,161.3,66,7.4,;52.8,174.3,63,8,</v>
       </c>
     </row>
-    <row r="80" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C80" t="str">
+        <f>PumpOG!B69</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D80" t="str">
+        <f>PumpOG!B69</f>
+        <v>SPSA</v>
+      </c>
       <c r="E80" t="str">
         <f>PumpOG!A69</f>
         <v>4/3-HD80D-METAL</v>
@@ -13472,7 +14012,15 @@
         <v>82,0,0,2.5,;81.6,10.5,30,2.5,;81,16,40,2.5,;80,23,50,3,;77,36,60,4.1,;73.4,48,65,6.3,;64,69,68,11,;55,84.3,65,16,</v>
       </c>
     </row>
-    <row r="81" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C81" t="str">
+        <f>PumpOG!B70</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D81" t="str">
+        <f>PumpOG!B70</f>
+        <v>SPSA</v>
+      </c>
       <c r="E81" t="str">
         <f>PumpOG!A70</f>
         <v>4/3-HD80D-METAL 6V</v>
@@ -13486,7 +14034,15 @@
         <v>94.8,0,0,4,;95.2,11,30,4.2,;95,16.1,40,4.5,;94.6,23.2,50,5.5,;92.5,32.9,60,6.8,;88.3,47.2,68,9,;84.3,58.4,72,10.8,;77.2,72.1,74.5,13.7,;69.7,87.4,71.89,17,</v>
       </c>
     </row>
-    <row r="82" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C82" t="str">
+        <f>PumpOG!B71</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D82" t="str">
+        <f>PumpOG!B71</f>
+        <v>SPSA</v>
+      </c>
       <c r="E82" t="str">
         <f>PumpOG!A71</f>
         <v>4/3-HD80D-RUBBER</v>
@@ -13500,7 +14056,15 @@
         <v>7.1,0,0,0.6,;7.2,3.1,30,0.5,;7.2,4.5,40,0.7,;7.1,7,50,0.8,;6.8,10.9,60,1.2,;6.1,16.5,62,1.6,;4.6,22.5,60,2.1,|15.2,0,0,0.65,;15.5,4.1,30,2,;15.5,9.3,50,1.8,;15.1,14,60,2.1,;13.2,24.5,64.9,3.7,;10.1,34.2,59.8,5.7,|27.3,0,0,2,;27.7,5.7,30,2,;27.8,7.9,40,2,;27.7,12.3,50,2.1,;27,18.4,60,2.9,;26.2,22.5,65,3.3,;23.4,32.8,67,5.3,;19.6,42.4,65,7.6,;18,46,60,8.6,|34.8,0,0,1.9,;35.2,6.5,30,2,;35.2,9,40,2,;34.9,13.9,50,2.2,;34,21,60,3.2,;33.1,25.9,65,4,;29.8,36.8,68,6.4,;25.1,47.3,65,9.1,;22.9,51.9,59.9,10.5,</v>
       </c>
     </row>
-    <row r="83" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C83" t="str">
+        <f>PumpOG!B72</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D83" t="str">
+        <f>PumpOG!B72</f>
+        <v>SPSA</v>
+      </c>
       <c r="E83" t="str">
         <f>PumpOG!A72</f>
         <v>4/3-HDM80C-METAL</v>
@@ -13514,7 +14078,15 @@
         <v>82,0,0,2.5,;81.6,10.5,30,2.5,;81,16,40,2.5,;80,23,50,3,;77,36,60,4.1,;73.4,48,65,6.3,;64,69,68,11,;55,84.3,65,16,</v>
       </c>
     </row>
-    <row r="84" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C84" t="str">
+        <f>PumpOG!B73</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D84" t="str">
+        <f>PumpOG!B73</f>
+        <v>SPSA</v>
+      </c>
       <c r="E84" t="str">
         <f>PumpOG!A73</f>
         <v>4/3-HDM80C-RUBBER</v>
@@ -13528,7 +14100,15 @@
         <v>7.1,0,0,0.6,;7.2,3.1,30,0.5,;7.2,4.5,40,0.7,;7.1,7,50,0.8,;6.8,10.9,60,1.2,;6.1,16.5,62,1.6,;4.6,22.5,60,2.1,|15.2,0,0,0.65,;15.5,4.1,30,2,;15.5,9.3,50,1.8,;15.1,14,60,2.1,;13.2,24.5,64.9,3.7,;10.1,34.2,59.8,5.7,|27.3,0,0,2,;27.7,5.7,30,2,;27.8,7.9,40,2,;27.7,12.3,50,2.1,;27,18.4,60,2.9,;26.2,22.5,65,3.3,;23.4,32.8,67,5.3,;19.6,42.4,65,7.6,;18,46,60,8.6,|34.8,0,0,1.9,;35.2,6.5,30,2,;35.2,9,40,2,;34.9,13.9,50,2.2,;34,21,60,3.2,;33.1,25.9,65,4,;29.8,36.8,68,6.4,;25.1,47.3,65,9.1,;22.9,51.9,59.9,10.5,</v>
       </c>
     </row>
-    <row r="85" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C85" t="str">
+        <f>PumpOG!B74</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D85" t="str">
+        <f>PumpOG!B74</f>
+        <v>SPSA</v>
+      </c>
       <c r="E85" t="str">
         <f>PumpOG!A74</f>
         <v>4/3-HDP80DD-METAL</v>
@@ -13542,7 +14122,15 @@
         <v>82,0,0,2.5,;81.6,10.5,30,2.5,;81,16,40,2.5,;80,23,50,3,;77,36,60,4.1,;73.4,48,65,6.3,;64,69,68,11,;55,84.3,65,16,</v>
       </c>
     </row>
-    <row r="86" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C86" t="str">
+        <f>PumpOG!B75</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D86" t="str">
+        <f>PumpOG!B75</f>
+        <v>SPSA</v>
+      </c>
       <c r="E86" t="str">
         <f>PumpOG!A75</f>
         <v>6 AHF</v>
@@ -13556,7 +14144,15 @@
         <v>11,0,0,1.1,;10.3,37.7,40,1.3,;10.2,53.5,50,1.4,;10.2,63.3,55,1.5,;10,80.3,60,1.6,;9.9,100.4,65,2.2,;9.6,112,67,2.3,;9.3,120.5,67.6,2.4,;9,130.8,67,2.6,;8.4,142.4,65,2.8,;7.4,157.6,60,3,;6.7,165.5,58,3.3,|26.5,0,0,1.1,;25.1,59,40,1.46,;24.8,82.8,50,1.8,;24.6,98.6,55,2.2,;24.3,118.7,60,2.4,;23.8,147.9,65,2.8,;23.2,169.8,67,3.3,;22.3,189.9,67.6,3.5,;21.5,205.7,67,3.8,;20,226.4,65,4,;17.7,250.7,60,4.7,;16.3,261.7,58,5,|39.1,0,0,1.1,;36.9,71.8,40,1.6,;36.5,100.4,50,2.1,;36.2,120.5,55,2.4,;35.9,143.6,60,3.8,;35.1,178.9,65,3.3,;34.2,204.5,67,3.7,;33,227.6,67.6,4,;31.4,251.3,67,4.5,;29.4,275.7,65,5.3,;26.2,306.1,60,5.5,</v>
       </c>
     </row>
-    <row r="87" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C87" t="str">
+        <f>PumpOG!B76</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D87" t="str">
+        <f>PumpOG!B76</f>
+        <v>SPSA</v>
+      </c>
       <c r="E87" t="str">
         <f>PumpOG!A76</f>
         <v>6/4-HD100E-METAL</v>
@@ -13570,7 +14166,15 @@
         <v>80,0,0,4.2,;80,26.5,40,4.2,;78.2,48,50,5,;76.4,61,60,5.8,;74.2,74,65,6.6,;70.2,95,68,8.2,;64,119,70,11.5,;56.3,147,68,0,</v>
       </c>
     </row>
-    <row r="88" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C88" t="str">
+        <f>PumpOG!B77</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D88" t="str">
+        <f>PumpOG!B77</f>
+        <v>SPSA</v>
+      </c>
       <c r="E88" t="str">
         <f>PumpOG!A77</f>
         <v>6/4-HD100E-RUBBER</v>
@@ -13584,7 +14188,15 @@
         <v>44.5,0,0,2.5,;44,20,40,2.5,;43.4,30,50,3,;42.15,44,60,3.5,;41,55,65,4,;38.9,72,70,4.5,;36,90,71,5.4,;33,106,70,0,;29.6,123,65,0,</v>
       </c>
     </row>
-    <row r="89" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C89" t="str">
+        <f>PumpOG!B78</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D89" t="str">
+        <f>PumpOG!B78</f>
+        <v>SPSA</v>
+      </c>
       <c r="E89" t="str">
         <f>PumpOG!A78</f>
         <v>6/4-HDM100D-METAL</v>
@@ -13598,7 +14210,15 @@
         <v>80,0,0,4.2,;80,26.5,40,4.2,;78.2,48,50,5,;76.4,61,60,5.8,;74.2,74,65,6.6,;70.2,95,68,8.2,;64,119,70,11.5,;56.3,147,68,0,</v>
       </c>
     </row>
-    <row r="90" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C90" t="str">
+        <f>PumpOG!B79</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D90" t="str">
+        <f>PumpOG!B79</f>
+        <v>SPSA</v>
+      </c>
       <c r="E90" t="str">
         <f>PumpOG!A79</f>
         <v>6/4-HDM100D-METAL 6V</v>
@@ -13612,7 +14232,15 @@
         <v>90,0,0,4.8,;89.9,28.5,40,4.8,;89.2,41.5,50,5.5,;88,57.5,60,6,;84.1,85,70,7.9,;80,110,75,9.8,;74,137.8,77,12.8,;66,167,75,,</v>
       </c>
     </row>
-    <row r="91" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C91" t="str">
+        <f>PumpOG!B80</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D91" t="str">
+        <f>PumpOG!B80</f>
+        <v>SPSA</v>
+      </c>
       <c r="E91" t="str">
         <f>PumpOG!A80</f>
         <v>6/4-HDM100D-RUBBER</v>
@@ -13626,7 +14254,15 @@
         <v>44.5,0,0,2.5,;44,20,40,2.5,;43.4,30,50,3,;42.15,44,60,3.5,;41,55,65,4,;38.9,72,70,4.5,;36,90,71,5.4,;33,106,70,0,;29.6,123,65,0,</v>
       </c>
     </row>
-    <row r="92" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C92" t="str">
+        <f>PumpOG!B81</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D92" t="str">
+        <f>PumpOG!B81</f>
+        <v>SPSA</v>
+      </c>
       <c r="E92" t="str">
         <f>PumpOG!A81</f>
         <v>6/4-HDP100EE-METAL</v>
@@ -13640,7 +14276,15 @@
         <v>80,0,0,4.2,;80,26.5,40,4.2,;78.2,48,50,5,;76.4,61,60,5.8,;74.2,74,65,6.6,;70.2,95,68,8.2,;64,119,70,11.5,;56.3,147,68,0,</v>
       </c>
     </row>
-    <row r="93" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C93" t="str">
+        <f>PumpOG!B82</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D93" t="str">
+        <f>PumpOG!B82</f>
+        <v>SPSA</v>
+      </c>
       <c r="E93" t="str">
         <f>PumpOG!A82</f>
         <v>7/3-HDF80C-METAL</v>
@@ -13654,7 +14298,15 @@
         <v>7,0,0,0,;7.1,5.9,30,0,;7.1,8.7,40,0,;7,12.3,50,0,;7,14.4,55,0,;6.9,16.2,58,0,;6.8,18.5,60,0,;6.6,22.6,61.9,0,;6.2,26.2,60,0,;5.9,28.8,58,0,;5.8,30.3,57,0,|28.1,0,0,0,;28.4,12.3,30,0,;28.4,17.5,40,0,;28,24.2,50,0,;27.8,28.8,55,0,;27.4,32.7,58,0,;27.1,36.2,60,0,;26.1,44.5,61.9,0,;24.9,52.8,60,0,;24.3,57.1,58,0,;23.6,61.5,57,0,|52.9,0,0,1.8,;53.6,17,30,1.8,;53.5,24.4,40,2.5,;53,33.9,50,2.5,;52.4,40.1,55,3.4,;51.9,45.2,58,3.8,;51.2,49.9,60,4.3,;49.5,61.3,61.9,4.5,;47.1,72.8,60,5.4,;45.8,78.5,58,6.3,;44.6,82.6,52,6.5,</v>
       </c>
     </row>
-    <row r="94" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C94" t="str">
+        <f>PumpOG!B83</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D94" t="str">
+        <f>PumpOG!B83</f>
+        <v>SPSA</v>
+      </c>
       <c r="E94" t="str">
         <f>PumpOG!A83</f>
         <v>8 AHF</v>
@@ -13668,7 +14320,15 @@
         <v>14.8,0,0,1.8,;14.8,64,40,1.8,;14.9,90.5,50,1.8,;14.8,135.2,60,1.8,;14.5,171.4,64,1.8,;14.1,199.2,66,1.8,;13.8,225.8,66.5,1.8,;13.1,262,66,1.9,;12.1,298.2,64,2,|33,0,0,2.4,;33.4,90.5,40,2.6,;33.3,129.2,50,2.7,;32.9,188.3,60,2.9,;32.5,230.6,64,3,;31.9,266.8,66,3.3,;31.2,298.2,67,3.5,;30.2,344.1,67.7,3.7,;29,380.3,67,3.9,;27.7,420.1,66,4.1,;26.1,467.2,64,4.4,|58.3,0,0,4,;58.8,118.3,40,4.4,;58.8,167.8,50,4.5,;58.3,243.9,60,5,;57.4,295.8,64,5.3,;56.4,339.2,66,5.6,;55.5,375.5,67,5.7,;53.3,443.1,67.7,6.2,;50.3,517.9,67,6.5,;48.1,561.4,66,6.8,;45.9,601.2,64,7,</v>
       </c>
     </row>
-    <row r="95" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C95" t="str">
+        <f>PumpOG!B84</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D95" t="str">
+        <f>PumpOG!B84</f>
+        <v>SPSA</v>
+      </c>
       <c r="E95" t="str">
         <f>PumpOG!A84</f>
         <v>8/6-HD150F-METAL</v>
@@ -13682,7 +14342,15 @@
         <v>80,0,0,2.5,;81.2,25,20,2.5,;81.8,60,40,3,;81.5,84,50,4,;80,121,60,5,;78,149,65,6,;74.2,189,70,8,;67.9,241,72,11,;61,285,70,14,</v>
       </c>
     </row>
-    <row r="96" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C96" t="str">
+        <f>PumpOG!B85</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D96" t="str">
+        <f>PumpOG!B85</f>
+        <v>SPSA</v>
+      </c>
       <c r="E96" t="str">
         <f>PumpOG!A85</f>
         <v>8/6-HD150F-METAL 6V</v>
@@ -13696,7 +14364,15 @@
         <v>90.6,0,0,6.1,;89.8,58.6,40,6.1,;88.8,86.7,50,6.1,;87.1,124.5,60,6.9,;83.5,175.1,70,8.7,;73.4,262.7,75,12.1,;56.5,350.2,70,16.1,</v>
       </c>
     </row>
-    <row r="97" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C97" t="str">
+        <f>PumpOG!B86</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D97" t="str">
+        <f>PumpOG!B86</f>
+        <v>SPSA</v>
+      </c>
       <c r="E97" t="str">
         <f>PumpOG!A86</f>
         <v>8/6-HD150F-RUBBER</v>
@@ -13710,7 +14386,15 @@
         <v>52,0,0,3.8,;51.6,42,40,3.8,;51,68,50,4,;49.8,95,60,4.8,;48.7,115,65,5.8,;46.3,152,70,7.6,;43,191,71,10,;39.5,230,70,0,;36,262,65,0,</v>
       </c>
     </row>
-    <row r="98" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C98" t="str">
+        <f>PumpOG!B87</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D98" t="str">
+        <f>PumpOG!B87</f>
+        <v>SPSA</v>
+      </c>
       <c r="E98" t="str">
         <f>PumpOG!A87</f>
         <v>8/6-HDM150E-METAL</v>
@@ -13724,7 +14408,15 @@
         <v>80,0,0,2.5,;81.2,25,20,2.5,;81.8,60,40,3,;81.5,84,50,4,;80,121,60,5,;78,149,65,6,;74.2,189,70,8,;67.9,241,72,11,;61,285,70,14,</v>
       </c>
     </row>
-    <row r="99" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C99" t="str">
+        <f>PumpOG!B88</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D99" t="str">
+        <f>PumpOG!B88</f>
+        <v>SPSA</v>
+      </c>
       <c r="E99" t="str">
         <f>PumpOG!A88</f>
         <v>8/6-HDM150E-RUBBER</v>
@@ -13738,7 +14430,15 @@
         <v>52,0,0,3.4,;51.6,42,40,3.8,;51.4,68,50,3.91,;49.8,94,60,4.5,;48.5,114,65,5.6,;46.2,152,70,6,;42.5,192,71,9.01,;39.5,230,70,13.7,;36,262,65,16,</v>
       </c>
     </row>
-    <row r="100" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C100" t="str">
+        <f>PumpOG!B89</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D100" t="str">
+        <f>PumpOG!B89</f>
+        <v>SPSA</v>
+      </c>
       <c r="E100" t="str">
         <f>PumpOG!A89</f>
         <v>8/6-HDP150FF-METAL</v>
@@ -13752,7 +14452,15 @@
         <v>80,0,0,2.5,;81.2,25,20,2.5,;81.8,60,40,3,;81.5,84,50,4,;80,121,60,5,;78,149,65,6,;74.2,189,70,8,;67.9,241,72,11,;61,285,70,14,</v>
       </c>
     </row>
-    <row r="101" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C101" t="str">
+        <f>PumpOG!B90</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D101" t="str">
+        <f>PumpOG!B90</f>
+        <v>SPSA</v>
+      </c>
       <c r="E101" t="str">
         <f>PumpOG!A90</f>
         <v>5/2-HDF50C-METAL</v>
@@ -13766,7 +14474,15 @@
         <v>8.4,0,0,2,;8.3,3.9,30,2,;8.3,5.7,40,2,;8.2,6.8,45,2,;8.1,8.2,50,2,;8,9.4,53,2.2,;7.8,10.7,55,2.3,;7.7,12.6,56.6,2.5,;7.3,15.1,55,2.8,;7.3,17.3,53,3.4,|33.8,0,0,2,;33.5,7.8,30,2,;33,11.4,40,2.4,;32.7,13.7,45,2.6,;32.1,16.5,50,3.2,;31.6,18.9,53,3.5,;31.1,21.3,55,3.9,;30.1,25.8,56.6,4.8,;28.8,30.8,55,6,;28.1,33.6,53,6.5,;27.8,35.6,52,51,|57.1,0,0,2,;56.5,10.1,30,2.3,;55.7,14.9,40,2.6,;55.1,17.8,45,3.4,;54.2,21.4,50,4,;53.2,24.4,53,4.5,;52.4,27.4,55,5.3,;50.6,33.3,56.6,6.3,;48.6,40.1,55,7,;47.4,43.9,53,7.4,;47,45.2,52,7.5,</v>
       </c>
     </row>
-    <row r="102" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C102" t="str">
+        <f>PumpOG!B91</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D102" t="str">
+        <f>PumpOG!B91</f>
+        <v>SPSA</v>
+      </c>
       <c r="E102" t="str">
         <f>PumpOG!A91</f>
         <v>4/3-HHD80E-METAL</v>
@@ -13780,7 +14496,15 @@
         <v>103.5,0,0,3,;101.5,17.2,30,2.55,;100.5,26,40,2.65,;99.2,39,50,3.75,;98.05,50,55,5,;95,68.1,60,7.5,;87,94,62.5,11.75,</v>
       </c>
     </row>
-    <row r="103" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C103" t="str">
+        <f>PumpOG!B92</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D103" t="str">
+        <f>PumpOG!B92</f>
+        <v>SPSA</v>
+      </c>
       <c r="E103" t="str">
         <f>PumpOG!A92</f>
         <v>6/4-HHD100F-METAL</v>
@@ -13794,7 +14518,15 @@
         <v>97.4,0,0,2.6,;95.7,29.8,30,2.6,;95,49.2,40,2.7,;93.9,71.1,50,3,;90.4,114.3,60,4.4,;88,133.2,63,5.3,;83.1,162,64,6.8,;75.8,191.3,63,9,;66,218.6,60,11.2,</v>
       </c>
     </row>
-    <row r="104" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C104" t="str">
+        <f>PumpOG!B93</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D104" t="str">
+        <f>PumpOG!B93</f>
+        <v>SPSA</v>
+      </c>
       <c r="E104" t="str">
         <f>PumpOG!A93</f>
         <v>8/6-HHD150G-METAL</v>
@@ -13808,7 +14540,15 @@
         <v>97.4,0,0,5.4,;96.2,69.2,30,5.4,;96.2,109.7,40,5.4,;95.8,135.6,45,5.7,;95.4,159.5,50,6,;94.2,200.1,55,6.5,;92.7,247.1,60,7.4,;87.5,325.5,65,9.4,;81.1,383.6,67,10.6,;76.7,417.7,65,11.7,</v>
       </c>
     </row>
-    <row r="105" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C105" t="str">
+        <f>PumpOG!B94</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D105" t="str">
+        <f>PumpOG!B94</f>
+        <v>SPSA</v>
+      </c>
       <c r="E105" t="str">
         <f>PumpOG!A94</f>
         <v>12/10-MD250F-RUBBER</v>
@@ -13822,7 +14562,15 @@
         <v>13.9,0,0,1.8,;12.4,50.5,30,2.1,;12.1,62.6,40,2.1,;11.8,80.8,50,2.5,;11.2,112.1,60,2.8,;10.5,141.4,65,3.1,;9.3,193.9,69,4.3,;6.8,263.6,65,5.9,|19.9,0,0,4.2,;18.5,46.5,30,4,;18.1,62.6,40,3.7,;17.4,89.9,50,3.8,;16.5,125.3,60,4.3,;16,151.5,65,4.5,;14.7,197,70,5.2,;13.6,235.4,70.98,5.9,;11.8,280.8,70,7.1,;9.8,320.2,65,8,|26.8,0,0,3.1,;25.3,52.5,30,3.1,;23.9,104,50,4,;22.8,145.5,60,4.3,;22.1,172.7,65,4.7,;20.6,221.2,70,5.7,;18.5,276.8,71.6,6.9,;15.9,331.3,70,8.6,;13.8,367.7,65,10,|44.5,0,0,5.4,;41.1,84.8,30,5.4,;40.1,110.1,40,5.4,;38.9,148.5,50,5.4,;37.2,200,60,5.9,;35.7,240.4,65,6.6,;33.5,297,70,8.3,;31,350.5,71.6,10.5,;26.8,419.2,70,14.2,;24.3,453.5,65,16.7,</v>
       </c>
     </row>
-    <row r="106" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C106" t="str">
+        <f>PumpOG!B95</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D106" t="str">
+        <f>PumpOG!B95</f>
+        <v>SPSA</v>
+      </c>
       <c r="E106" t="str">
         <f>PumpOG!A95</f>
         <v>14/12-MD300F-METAL</v>
@@ -13836,7 +14584,15 @@
         <v>11.6,0,0,1.8,;11.4,57.2,40,2.2,;11,105.1,60,1.4,;10.3,156.8,70,2.2,;9.7,208.4,75,2.2,;8.6,269.3,78,2.5,;6.9,361.5,75,3.8,|35.7,0,0,0,;35.1,99.6,40,0,;33.8,186.3,60,0,;32.3,256.4,70,0,;30.7,317.2,75,0,;28.8,385.5,78,0,;26.5,461.1,79,0,;23.3,558.8,78,0,;21,634.4,75,0,|65.6,0,0,3.4,;64.5,136.5,40,3.1,;62.2,252.7,60,4.5,;59.4,350.4,70,6.1,;56.2,442.6,75,7.7,;53.4,516.4,78,9.5,;48.7,632.6,79,12.3,;42.9,761.7,78,15.7,;38.4,859.4,75,18.6,</v>
       </c>
     </row>
-    <row r="107" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C107" t="str">
+        <f>PumpOG!B96</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D107" t="str">
+        <f>PumpOG!B96</f>
+        <v>SPSA</v>
+      </c>
       <c r="E107" t="str">
         <f>PumpOG!A96</f>
         <v>16/14-MD350F-METAL</v>
@@ -13850,7 +14606,15 @@
         <v>13.9,0,0,2,;14.2,66.9,40,2.1,;14.1,94.1,50,2,;13.9,129.7,60,2,;13.4,184.1,70,2.1,;13.1,223.8,75,2,;12,295,80,2.1,;10.8,357.7,81,2.7,;9.8,424.7,80,3.2,|61.1,0,0,7.7,;61.6,144.4,40,7.5,;61.1,200.8,50,7.7,;60.5,274.1,60,7.7,;58.6,384.9,70,8.2,;56.6,472.8,75,8.8,;52.2,619.2,80,10.5,;47.5,761.5,81,12.7,;42.8,889.1,80,15.4,</v>
       </c>
     </row>
-    <row r="108" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C108" t="str">
+        <f>PumpOG!B97</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D108" t="str">
+        <f>PumpOG!B97</f>
+        <v>SPSA</v>
+      </c>
       <c r="E108" t="str">
         <f>PumpOG!A97</f>
         <v>10/8-MC200FF-RUBBER</v>
@@ -13864,7 +14628,15 @@
         <v>71.4,0,0,3.5,;72.8,357.9,50,3.7,;72.2,479.6,60,4,;70.2,723,73,4.67,;67.6,916.3,78,5.5,;63.4,1181,80.1,6.8,;58.7,1450,78,8,;56.9,1554,76,9.6,;56.3,1579,77,10,</v>
       </c>
     </row>
-    <row r="109" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C109" t="str">
+        <f>PumpOG!B98</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D109" t="str">
+        <f>PumpOG!B98</f>
+        <v>SPSA</v>
+      </c>
       <c r="E109" t="str">
         <f>PumpOG!A98</f>
         <v>26/22-ESHR550</v>
@@ -13878,7 +14650,15 @@
         <v>71.1,0,0,0,;70.8,2527,60,4.4,;69.8,3370,70,4.4,;68.9,3940,75,4.6,;67.4,4728,80,5.1,;65.8,5408,83,5.5,;63.7,6169,85,6.2,;60.2,7283,85.1,7.2,;56.2,8342,85,7.6,;53.2,9049,83,7.8,;49.8,9837,81,8.5,</v>
       </c>
     </row>
-    <row r="110" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C110" t="str">
+        <f>PumpOG!B99</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D110" t="str">
+        <f>PumpOG!B99</f>
+        <v>SPSA</v>
+      </c>
       <c r="E110" t="str">
         <f>PumpOG!A99</f>
         <v>30/26-ESH650</v>
@@ -13892,7 +14672,15 @@
         <v>59,0,0,0,;57.7,3679,60,3,;56.3,4821,70,3.5,;55.2,5607,75,4,;53.7,6643,80,4.3,;52,7536,83,4.7,;50.1,8536,85,5.4,;46.8,10179,85.2,6.5,;42.7,12036,85,7.6,;40,13250,83,8,;38.3,14000,81,8.5,</v>
       </c>
     </row>
-    <row r="111" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C111" t="str">
+        <f>PumpOG!B100</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D111" t="str">
+        <f>PumpOG!B100</f>
+        <v>SPSA</v>
+      </c>
       <c r="E111" t="str">
         <f>PumpOG!A100</f>
         <v>36/30-MC750V-RUBBER</v>
@@ -13906,7 +14694,15 @@
         <v>62.6,0,0,3,;60.9,6061,60,3,;59.6,7935,70,3.5,;57.8,9974,78,3.98,;55.2,12288,84,4.5,;52.5,14327,87,5.4,;50.9,15539,88,5.8,;48.5,17137,88.5,7,;45.8,18790,88,7.5,;43.7,20002,87,8,;40.4,22096,84,8.5,;39.1,22922,83,9,</v>
       </c>
     </row>
-    <row r="112" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C112" t="str">
+        <f>PumpOG!B101</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D112" t="str">
+        <f>PumpOG!B101</f>
+        <v>SPSA</v>
+      </c>
       <c r="E112" t="str">
         <f>PumpOG!A101</f>
         <v>10/8-MD200F-METAL</v>
@@ -13920,7 +14716,15 @@
         <v>66.3,0,0,3.8,;65,84,40,3.8,;63.9,124,50,3.8,;61,186,60,3.8,;58.8,225,65,4,;55.6,282,70,4.6,;49.5,367,73,6.1,;42.8,440,70,7.5,;38.4,481,65,8.4,</v>
       </c>
     </row>
-    <row r="113" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C113" t="str">
+        <f>PumpOG!B102</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D113" t="str">
+        <f>PumpOG!B102</f>
+        <v>SPSA</v>
+      </c>
       <c r="E113" t="str">
         <f>PumpOG!A102</f>
         <v>10/8-MD200F-RUBBER</v>
@@ -13934,7 +14738,15 @@
         <v>44.3,0,0,4.74,;43.9,50,40,4.74,;43.5,76,50,5.2,;42.7,111,60,6.5,;41.3,161,70,9.9,;39.7,208,75,14.3,;35.5,302,79,0,;30.4,375,75,0,</v>
       </c>
     </row>
-    <row r="114" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="114" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C114" t="str">
+        <f>PumpOG!B103</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D114" t="str">
+        <f>PumpOG!B103</f>
+        <v>SPSA</v>
+      </c>
       <c r="E114" t="str">
         <f>PumpOG!A103</f>
         <v>12/10-MD250F-METAL</v>
@@ -13948,7 +14760,15 @@
         <v>49.7,0,0,6,;48.3,86,40,6,;47.2,130,50,6.3,;44.5,202,60,7,;42.7,240,65,7.6,;39.2,300,70,10,;33.8,383,73,11,;29.5,442,70,13,;25,499,64.8,0,</v>
       </c>
     </row>
-    <row r="115" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C115" t="str">
+        <f>PumpOG!B104</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D115" t="str">
+        <f>PumpOG!B104</f>
+        <v>SPSA</v>
+      </c>
       <c r="E115" t="str">
         <f>PumpOG!A104</f>
         <v>14/12-MD300F-RUBBER</v>
@@ -13962,7 +14782,15 @@
         <v>43.4,0,0,3.9,;43.2,80,35,3.9,;42,182,60,4,;40.5,250,70,4.2,;39,307,75,5,;32.6,495,81,6,;25,662,75,7.3,</v>
       </c>
     </row>
-    <row r="116" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="116" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C116" t="str">
+        <f>PumpOG!B105</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D116" t="str">
+        <f>PumpOG!B105</f>
+        <v>SPSA</v>
+      </c>
       <c r="E116" t="str">
         <f>PumpOG!A105</f>
         <v>150 MP-M</v>
@@ -13976,7 +14804,15 @@
         <v>11.9,0,0,0,;12.1,33.7,40,0,;11.9,50.8,50,0,;11.2,75,60,0,;10.4,91.5,65,0,;9.2,120.8,72,0,;8.7,134.7,70,0,|17.1,0,0,0,;17.1,37.5,40,0,;17.1,46.4,45,0,;16.8,66.7,55,0,;15.7,97.2,65,0,;14.1,128.4,72,0,;12.5,155.7,70,0,|23.2,0,0,0,;23.2,42.6,40,0,;23.2,61,50,0,;22.6,85.2,60,0,;21.9,103.6,65,0,;19.9,137.3,72,0,;17.9,169.1,70,0,|30.4,0,0,0,;30.7,47,40,0,;30.3,66.1,50,0,;29.5,92.2,60,0,;28.9,110,65,0,;26.7,146.8,72,0,;23.5,184.3,70,0,|38.4,0,0,0,;38.5,52.1,40,0,;38.5,61,45,0,;38,83.9,55,0,;36.7,117.6,65,0,;34.1,157.6,72,0,;29.5,202.1,70,0,|47.2,0,0,0,;47.2,57.2,40,0,;46.8,77.5,50,0,;46,105.5,60,0,;45.1,126.5,65,0,;42.5,171,72,0,;36.1,220.6,70,0,|56.8,0,0,0,;57.3,62.3,40,0,;57,73.1,45,0,;56.2,98.5,55,0,;54.6,138.6,65,0,;51.2,188.1,71.5,0,;43.7,241.5,70,0,|67.4,0,0,0,;68.1,68,40,0,;67.5,92.2,50,0,;66.2,127.1,60,0,;64.8,155.1,65,0,;60.2,211.7,72,0,;51.6,263.1,70,0,|78.2,0,0,3.8,;79.9,73,40,3.8,;79.9,86,45,4,;79.6,101,50,4.5,;78.9,120,55,5,;77.6,145,60,5.6,;74.9,183.5,67,6.8,;67.5,248,72.5,11,;60.5,284,70,13.9,</v>
       </c>
     </row>
-    <row r="117" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="117" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C117" t="str">
+        <f>PumpOG!B106</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D117" t="str">
+        <f>PumpOG!B106</f>
+        <v>SPSA</v>
+      </c>
       <c r="E117" t="str">
         <f>PumpOG!A106</f>
         <v>16/14-MD350F-RUBBER</v>
@@ -13990,7 +14826,15 @@
         <v>45,0,0,2.4,;45,54,20,2.4,;45,122.4,40,2.4,;44.4,225,60,2.9,;43.5,307.8,70,3.4,;41.6,444.6,80,4.4,;39.4,565.2,85,5.7,;35.1,730.8,86.5,8.1,;31.7,837,85,9.7,</v>
       </c>
     </row>
-    <row r="118" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="118" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C118" t="str">
+        <f>PumpOG!B107</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D118" t="str">
+        <f>PumpOG!B107</f>
+        <v>SPSA</v>
+      </c>
       <c r="E118" t="str">
         <f>PumpOG!A107</f>
         <v>MDP125</v>
@@ -14004,7 +14848,15 @@
         <v>29.9,0,0,0,;30.6,63.7,50,0,;29.9,115.9,65,0,;26.5,191,70,0,;20.4,253.1,66,0,|59,0,0,0,;60.5,75.1,50,0,;60.2,133.9,65,0,;56.5,213.9,75,0,;54.1,246.5,77,0,;50.3,280.8,75,0,;40.5,351,65,0,|96.6,0,0,0,;100.3,86.5,50,0,;100,151.8,65,0,;97.3,222,75,0,;88.8,315.1,79,0,;74.1,413.1,75,0,;67,450.6,73,0,|144.2,0,0,0,;149.3,99.6,50,0,;149.3,169.8,65,0,;147.3,241.6,75,0,;143.2,295.5,80,0,;133,383.7,83.55,0,;117,475.1,80,0,;99.7,551.8,73,0,|172.4,0,0,0,;177.9,111,50,0,;178.2,181.2,65,0,;175.9,251.4,75,0,;172.1,305.3,80,0,;167,354.3,83,0,;162.9,386.9,84,0,;158.2,421.2,84.42,0,;152.4,458.8,84,0,;146.3,488.2,83,0,;134,542,80,0,;118.7,604.1,73,0,</v>
       </c>
     </row>
-    <row r="119" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="119" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C119" t="str">
+        <f>PumpOG!B108</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D119" t="str">
+        <f>PumpOG!B108</f>
+        <v>SPSA</v>
+      </c>
       <c r="E119" t="str">
         <f>PumpOG!A108</f>
         <v>MDP150</v>
@@ -14018,7 +14870,15 @@
         <v>211.1,0,0,0,;220.6,282.8,56,0,;222.2,462.3,65,0,;216.1,656.6,74,0,;208.9,769.7,78,0,;202.2,850.8,80,0,;183.2,1006,81.3,0,;167.6,1109,80,0,;161,1146,79,0,;149.3,1207,77,0,</v>
       </c>
     </row>
-    <row r="120" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="120" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C120" t="str">
+        <f>PumpOG!B109</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D120" t="str">
+        <f>PumpOG!B109</f>
+        <v>SPSA</v>
+      </c>
       <c r="E120" t="str">
         <f>PumpOG!A109</f>
         <v>MDP150C</v>
@@ -14032,7 +14892,15 @@
         <v>211.8,0,0,0,;210.8,140.6,47,0,;209.9,223.8,58,0,;207.1,308.4,67,0,;203.3,383,73,0,;199.5,431.8,76,0,;191.1,504.9,79,0,;177.4,595.3,80.1,0,;164.2,659.8,79,0,;157.2,687.1,78,0,;150.6,714.3,75,0,</v>
       </c>
     </row>
-    <row r="121" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="121" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C121" t="str">
+        <f>PumpOG!B110</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D121" t="str">
+        <f>PumpOG!B110</f>
+        <v>SPSA</v>
+      </c>
       <c r="E121" t="str">
         <f>PumpOG!A110</f>
         <v>10/8 P-M</v>
@@ -14046,7 +14914,15 @@
         <v>20.5,0,0,4,;19.5,60,50,4,;18,120,68,6,;15.8,180,73.5,9,;12,255,69.5,11.5,|36,0,0,4,;35.5,36,30,4,;33.5,105,57.5,6,;31,171,70,9,;27.5,243,73.5,11.5,;23.5,306,70,14,|55,0,0,0,;54.5,45,30,0,;51,150,60,0,;47,231,70,0,;42,306,73.5,0,;37.5,366,70,0,|66.5,0,0,4,;65.5,75,40,4,;62,168,60,6,;56,270,70,9,;51,336,74,11.5,;45.5,405,69.5,14,</v>
       </c>
     </row>
-    <row r="122" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C122" t="str">
+        <f>PumpOG!B111</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D122" t="str">
+        <f>PumpOG!B111</f>
+        <v>SPSA</v>
+      </c>
       <c r="E122" t="str">
         <f>PumpOG!A111</f>
         <v>100 MP-M</v>
@@ -14060,7 +14936,15 @@
         <v>80,0,0,1.3,;80,26.5,40,1.3,;78.2,48,50,2,;76.4,61,60,3.1,;74.2,74,65,4.1,;70.2,95,68,5.9,;64,119,70,9.5,;56.3,147,68,14,</v>
       </c>
     </row>
-    <row r="123" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="123" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C123" t="str">
+        <f>PumpOG!B112</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D123" t="str">
+        <f>PumpOG!B112</f>
+        <v>SPSA</v>
+      </c>
       <c r="E123" t="str">
         <f>PumpOG!A112</f>
         <v>12/10 P-M</v>
@@ -14074,7 +14958,15 @@
         <v>11.9,0,0,1.7,;11.5,48.5,40,1.6,;11.4,65.9,50,1.8,;11,92.4,60,1.9,;10.5,125.3,70,2.1,;10,158.2,75,2.3,;8.7,195.7,76.85,2.5,;7.7,223.2,75.75,2.7,|31.5,0,0,0,;30.5,86,40,0,;29.9,117.1,50,0,;28.8,158.2,60,0,;27.4,200.3,70,0,;25.8,242.4,75,0,;24,278,78,0,;22.7,304.6,78.5,0,;20.4,337.5,78,0,|50,0,0,3.7,;48.5,85.1,40,3.7,;47.3,124.4,50,3.9,;45.6,176.5,60,4.2,;43.3,236.9,70,5.2,;40.9,286.3,75,6.1,;38.5,330.2,78,7.2,;35.3,380.5,78.8,8.8,;32.1,420.7,77.95,10.1,</v>
       </c>
     </row>
-    <row r="124" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="124" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C124" t="str">
+        <f>PumpOG!B113</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D124" t="str">
+        <f>PumpOG!B113</f>
+        <v>SPSA</v>
+      </c>
       <c r="E124" t="str">
         <f>PumpOG!A113</f>
         <v>2/1.5 P-M</v>
@@ -14088,7 +14980,15 @@
         <v>2.7,0,0,0,;2.3,2.3,20,0,;2.1,3.3,27,0,;1.9,3.9,30,0,;1.5,4.9,27,0,|4.2,0,0,0,;3.6,2.1,20,0,;3.1,3.7,30,0,;2.9,4.4,32,0,;2.3,5.6,30,0,|8.8,0,0,0,;8.5,1.8,20,0,;8.1,3.3,30,0,;7,6,35,0,;5.6,7.9,30,0,|15.6,0,0,0,;15.2,1.8,20,0,;15,3.1,30,0,;14.2,5.3,40,0,;12.6,7.7,43,0,;9.6,10.3,39.5,0,|24.2,0,0,0,;23.8,2,20,0,;23.4,3.2,30,0,;22.6,4.9,39.5,0,;21.6,6.6,45,0,;19.4,9.4,47,0,;16.8,12.1,45,0,;14.6,13.8,39.5,0,|34.6,0,0,0,;34.4,2.1,20,0,;34,3.6,30,0,;32.6,6,40,0,;31,8.3,45,0,;28.4,11.1,49,0,;25,14.2,45,0,;22.1,16.5,39.5,0,</v>
       </c>
     </row>
-    <row r="125" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="125" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C125" t="str">
+        <f>PumpOG!B114</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D125" t="str">
+        <f>PumpOG!B114</f>
+        <v>SPSA</v>
+      </c>
       <c r="E125" t="str">
         <f>PumpOG!A114</f>
         <v>50 MP-M</v>
@@ -14102,7 +15002,15 @@
         <v>18,0,0,0,;17,4,30,0,;16.4,5.4,35,0,;15.2,7.5,40,0,;13.5,9.6,41,0,;12,11,40,0,|22.9,0,0,0,;21.9,4.3,30,0,;21.4,5.7,35,0,;20.2,7.6,40,0,;18,10.2,40.98,0,;15.3,12.7,40,0,|28.7,0,0,0,;27.4,4.6,30,0,;26.8,6,35,0,;25.9,7.9,40,0,;24.2,9.8,43,0,;23,11.2,43.85,0,;20.6,13.1,43,0,;18.8,14.4,42,0,|34.8,0,0,0,;33.6,4.9,30,0,;33.1,6.3,35,0,;32,8.2,40,0,;30.7,9.9,43,0,;29.8,10.8,44,0,;28.3,12.3,44.5,0,;26,14.2,44,0,;24.5,15.1,43,0,;22.8,16.2,42,0,|41.6,0,0,0,;40.5,5.2,30,0,;39.7,6.6,35,0,;38.6,8.5,40,0,;37.3,10.2,43,0,;36.7,11.1,44,0,;35.2,12.4,45,0,;33.8,13.7,45.3,0,;32.1,15,45,0,;30.2,16.2,44,0,;28.8,17,43,0,;26.9,18.1,42,0,|49,0,0,0,;47.8,5.4,30,0,;47.1,6.9,35,0,;45.9,9,40,0,;44.5,10.8,43,0,;43.7,11.7,44,0,;42.4,13,45,0,;39.3,15.5,45.5,0,;36.4,17.3,45,0,;34.4,18.4,44,0,;32.9,19.3,43,0,;31.3,20,42,0,|57.1,0,0,3.4,;55.8,5.3,30,3.4,;55.1,7.05,35,3.6,;53.8,9.5,40,3.7,;52,11.8,43,4,;50.6,13,44,4.2,;48.6,14.6,45,4.4,;44,17.7,46,4.87,;39.9,20.08,45,5.4,;37,21.3,44,5.8,;35.1,22.08,43,6,</v>
       </c>
     </row>
-    <row r="126" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="126" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C126" t="str">
+        <f>PumpOG!B115</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D126" t="str">
+        <f>PumpOG!B115</f>
+        <v>SPSA</v>
+      </c>
       <c r="E126" t="str">
         <f>PumpOG!A115</f>
         <v>50 MP-M</v>
@@ -14116,7 +15024,15 @@
         <v>18,0,0,0,;17,4,30,0,;16.4,5.4,35,0,;15.2,7.5,40,0,;13.5,9.6,41,0,;12,11,40,0,|22.9,0,0,0,;21.9,4.3,30,0,;21.4,5.7,35,0,;20.2,7.6,40,0,;18,10.2,40.98,0,;15.3,12.7,40,0,|28.7,0,0,0,;27.4,4.6,30,0,;26.8,6,35,0,;25.9,7.9,40,0,;24.2,9.8,43,0,;23,11.2,43.85,0,;20.6,13.1,43,0,;18.8,14.4,42,0,|34.8,0,0,0,;33.6,4.9,30,0,;33.1,6.3,35,0,;32,8.2,40,0,;30.7,9.9,43,0,;29.8,10.8,44,0,;28.3,12.3,44.5,0,;26,14.2,44,0,;24.5,15.1,43,0,;22.8,16.2,42,0,|41.6,0,0,0,;40.5,5.2,30,0,;39.7,6.6,35,0,;38.6,8.5,40,0,;37.3,10.2,43,0,;36.7,11.1,44,0,;35.2,12.4,45,0,;33.8,13.7,45.3,0,;32.1,15,45,0,;30.2,16.2,44,0,;28.8,17,43,0,;26.9,18.1,42,0,|49,0,0,0,;47.8,5.4,30,0,;47.1,6.9,35,0,;45.9,9,40,0,;44.5,10.8,43,0,;43.7,11.7,44,0,;42.4,13,45,0,;39.3,15.5,45.5,0,;36.4,17.3,45,0,;34.4,18.4,44,0,;32.9,19.3,43,0,;31.3,20,42,0,|57.1,0,0,3.4,;55.8,5.3,30,3.4,;55.1,7.05,35,3.6,;53.8,9.5,40,3.7,;52,11.8,43,4,;50.6,13,44,4.2,;48.6,14.6,45,4.4,;44,17.7,46,4.87,;39.9,20.08,45,5.4,;37,21.3,44,5.8,;35.1,22.08,43,6,</v>
       </c>
     </row>
-    <row r="127" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="127" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C127" t="str">
+        <f>PumpOG!B116</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D127" t="str">
+        <f>PumpOG!B116</f>
+        <v>SPSA</v>
+      </c>
       <c r="E127" t="str">
         <f>PumpOG!A116</f>
         <v>75 MP-M</v>
@@ -14130,7 +15046,15 @@
         <v>82,0,0,3.7,;81.6,10.5,30,3.7,;81,16,40,3.8,;80,23,50,4,;77,36,60,5.6,;73.4,48,65,7.5,;64,69,68,11.6,;55,84.3,65,14.5,</v>
       </c>
     </row>
-    <row r="128" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="128" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C128" t="str">
+        <f>PumpOG!B117</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D128" t="str">
+        <f>PumpOG!B117</f>
+        <v>SPSA</v>
+      </c>
       <c r="E128" t="str">
         <f>PumpOG!A117</f>
         <v>24/16-DN600H-METAL</v>
@@ -14144,7 +15068,15 @@
         <v>79.9,0,0,1.5,;79,1927,40,3.1,;78.4,2922,57,3.8,;77.2,4299,72,4.7,;76.2,5188,78,4.8,;74.5,6395,82,5,;72,7581,84.5,6,;69.7,8471,84,0,;68.2,9021,82.5,0,;67,9424,81.5,0,</v>
       </c>
     </row>
-    <row r="129" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="129" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C129" t="str">
+        <f>PumpOG!B118</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D129" t="str">
+        <f>PumpOG!B118</f>
+        <v>SPSA</v>
+      </c>
       <c r="E129" t="str">
         <f>PumpOG!A118</f>
         <v>24/16-MST600H-CR35</v>
@@ -14158,7 +15090,15 @@
         <v>79.9,0,0,1.5,;79,1927,40,3.1,;78.4,2922,57,3.8,;77.2,4299,72,4.7,;76.2,5188,78,4.8,;74.5,6395,82,5,;72,7581,84.5,6,;69.7,8471,84,0,;68.2,9021,82.5,0,;67,9424,81.5,0,</v>
       </c>
     </row>
-    <row r="130" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="130" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C130" t="str">
+        <f>PumpOG!B119</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D130" t="str">
+        <f>PumpOG!B119</f>
+        <v>SPSA</v>
+      </c>
       <c r="E130" t="str">
         <f>PumpOG!A119</f>
         <v>20/18-DN500H-METAL</v>
@@ -14172,7 +15112,15 @@
         <v>77.6,0,0,0,;78,864,31,0,;77.8,1693,50,0,;77.2,2134,60,0,;76.4,2786,70,0,;74.3,3879,78,0,;71.5,4814,81,0,;68.6,5678,81.5,0,;64.8,6665,81,0,;60.8,7617,80,0,;59,8005,77,0,</v>
       </c>
     </row>
-    <row r="131" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="131" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C131" t="str">
+        <f>PumpOG!B120</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D131" t="str">
+        <f>PumpOG!B120</f>
+        <v>SPSA</v>
+      </c>
       <c r="E131" t="str">
         <f>PumpOG!A120</f>
         <v>20/18-MST-DN500H-M</v>
@@ -14186,7 +15134,15 @@
         <v>77.6,0,0,0,;78,864,31,0,;77.8,1693,50,0,;77.2,2134,60,0,;76.4,2786,70,0,;74.3,3879,78,0,;71.5,4814,81,0,;68.6,5678,81.5,0,;64.8,6665,81,0,;60.8,7617,80,0,;59,8005,77,0,</v>
       </c>
     </row>
-    <row r="132" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="132" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C132" t="str">
+        <f>PumpOG!B121</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D132" t="str">
+        <f>PumpOG!B121</f>
+        <v>SPSA</v>
+      </c>
       <c r="E132" t="str">
         <f>PumpOG!A121</f>
         <v>10 TC</v>
@@ -14200,7 +15156,15 @@
         <v>39,0,0,0,;35.3,102,37,,;34.5,124,40,,;33.6,148,41,,;31,209,43.5,,;28.3,264,42,,;25.3,332,40,,;22.25,406,37,,</v>
       </c>
     </row>
-    <row r="133" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="133" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C133" t="str">
+        <f>PumpOG!B122</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D133" t="str">
+        <f>PumpOG!B122</f>
+        <v>SPSA</v>
+      </c>
       <c r="E133" t="str">
         <f>PumpOG!A122</f>
         <v>2 TC</v>
@@ -14214,7 +15178,15 @@
         <v>23.3,0,0,0,;22.7,3.4,20,,;21.95,6.15,30,,;21.28,8.2,35,,;19.65,12,40,,;18,15,41,,;16.2,17.45,40,,</v>
       </c>
     </row>
-    <row r="134" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="134" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C134" t="str">
+        <f>PumpOG!B123</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D134" t="str">
+        <f>PumpOG!B123</f>
+        <v>SPSA</v>
+      </c>
       <c r="E134" t="str">
         <f>PumpOG!A123</f>
         <v>3 TC</v>
@@ -14228,7 +15200,15 @@
         <v>38.9,0,0,0,;38.2,4,10,,;37.65,6.4,15,,;37.3,8.95,20,,;36.9,12,25,,;36.5,15.5,30,,;35.8,20.4,35,,;34.7,26.2,39,,;33.5,31.5,41,,;31.7,38,41.5,,;29,45.5,41,,</v>
       </c>
     </row>
-    <row r="135" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="135" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C135" t="str">
+        <f>PumpOG!B124</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D135" t="str">
+        <f>PumpOG!B124</f>
+        <v>SPSA</v>
+      </c>
       <c r="E135" t="str">
         <f>PumpOG!A124</f>
         <v>4 TC</v>
@@ -14242,7 +15222,15 @@
         <v>38.9,0,0,0,;38.2,4,10,,;37.65,6.4,15,,;37.3,8.95,20,,;36.9,12,25,,;36.5,15.5,30,,;35.8,20.4,35,,;34.7,26.2,39,,;33.5,31.5,41,,;31.7,38,41.5,,;29,45.5,41,,</v>
       </c>
     </row>
-    <row r="136" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="136" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C136" t="str">
+        <f>PumpOG!B125</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D136" t="str">
+        <f>PumpOG!B125</f>
+        <v>SPSA</v>
+      </c>
       <c r="E136" t="str">
         <f>PumpOG!A125</f>
         <v>6 TC</v>
@@ -14256,7 +15244,15 @@
         <v>39.8,0,0,0,;39.3,14.4,20,,;38.9,24.7,30,,;37.45,41,40,,;36,54,45,,;34,69.4,50,,;32,84.5,53,,;28.85,107.2,45,,</v>
       </c>
     </row>
-    <row r="137" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="137" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C137" t="str">
+        <f>PumpOG!B126</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D137" t="str">
+        <f>PumpOG!B126</f>
+        <v>SPSA</v>
+      </c>
       <c r="E137" t="str">
         <f>PumpOG!A126</f>
         <v>8 TC</v>
@@ -14270,7 +15266,15 @@
         <v>35,0,0,0,;34.2,22.5,20,,;33.5,39,30,,;32.9,52,35,,;31.35,72,40,,;28.1,104,42,,;23.7,141.5,40,,</v>
       </c>
     </row>
-    <row r="138" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="138" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C138" t="str">
+        <f>PumpOG!B127</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D138" t="str">
+        <f>PumpOG!B127</f>
+        <v>SPSA</v>
+      </c>
       <c r="E138" t="str">
         <f>PumpOG!A127</f>
         <v>3 TV</v>
@@ -14284,7 +15288,15 @@
         <v>9.6,0,0,0,;8,8.8,35,0,;7.1,12.2,39,0,;4.4,18.2,35,0,;2.5,21.2,32,0,|14.5,0,0,0,;13.5,7.8,35,0,;12.7,10.7,40,0,;10.9,15.1,43,0,;8.2,19.8,40,0,;6.2,23,35,0,;5.1,24.9,33,0,|20.6,0,0,0,;19.5,8.7,35,0,;18.8,11.3,40,0,;16.9,16,45,0,;15.7,18.1,45.35,0,;14.3,20.5,45,0,;11.2,24.6,40,0,;9.1,27.6,35,0,;8.2,28.9,33,0,|28,0,0,0,;26.2,11,35,0,;25.55,13.19,40,0,;23.75,17.4,45,0,;21.5,21,46.5,0,;18.75,24.9,45,0,;15.05,29.2,40,0,;12.8,32.1,35,0,;12.2,32.9,33,0,</v>
       </c>
     </row>
-    <row r="139" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="139" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C139" t="str">
+        <f>PumpOG!B128</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D139" t="str">
+        <f>PumpOG!B128</f>
+        <v>SPSA</v>
+      </c>
       <c r="E139" t="str">
         <f>PumpOG!A128</f>
         <v>VS100R-METAL</v>
@@ -14298,7 +15310,15 @@
         <v>50.2,0,0,0,;50,13,20,0,;49.6,21,30,0,;48.8,32,40,0,;48.1,39,45,0,;46.8,49,50,0,;43.9,68,55,0,;40.7,83.5,56,0,;35.5,104.5,55,0,</v>
       </c>
     </row>
-    <row r="140" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C140" t="str">
+        <f>PumpOG!B129</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D140" t="str">
+        <f>PumpOG!B129</f>
+        <v>SPSA</v>
+      </c>
       <c r="E140" t="str">
         <f>PumpOG!A129</f>
         <v>VS100R-RUBBER</v>
@@ -14312,7 +15332,15 @@
         <v>51.9,0,0,0,;51.25,17.5,30,0,;50.8,26,40,0,;50,38,50,0,;49.2,47,55,0,;47.3,62.3,60,0,;42.8,84.8,62,0,;37,106,60,0,</v>
       </c>
     </row>
-    <row r="141" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="141" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C141" t="str">
+        <f>PumpOG!B130</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D141" t="str">
+        <f>PumpOG!B130</f>
+        <v>SPSA</v>
+      </c>
       <c r="E141" t="str">
         <f>PumpOG!A130</f>
         <v>VS150S-METAL</v>
@@ -14326,7 +15354,15 @@
         <v>37.3,0,0,0,;37.2,22,20,0,;36.86,35.2,30,0,;36,54,40,0,;35.35,65,45,0,;34.15,82,50,0,;33.45,90.5,52,0,;29.2,135.5,55,0,;24.4,181,51.89,0,</v>
       </c>
     </row>
-    <row r="142" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="142" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C142" t="str">
+        <f>PumpOG!B131</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D142" t="str">
+        <f>PumpOG!B131</f>
+        <v>SPSA</v>
+      </c>
       <c r="E142" t="str">
         <f>PumpOG!A131</f>
         <v>VS200S-METAL</v>
@@ -14340,7 +15376,15 @@
         <v>40.8,0,0,0,;39.2,52,30,0,;38.4,75,40,0,;37.15,105.5,50,0,;35.2,141,58,0,;33.5,172,62,0,;30.1,228,64,0,;26.05,292,61.95,0,</v>
       </c>
     </row>
-    <row r="143" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="143" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C143" t="str">
+        <f>PumpOG!B132</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D143" t="str">
+        <f>PumpOG!B132</f>
+        <v>SPSA</v>
+      </c>
       <c r="E143" t="str">
         <f>PumpOG!A132</f>
         <v>VS40P-METAL</v>
@@ -14354,7 +15398,15 @@
         <v>5.9,0,0,0,;5.7,2.1,20,0,;5.1,3.8,30,0,;4.2,5.7,33,0,;3.3,7.4,31,0,|8.7,0,0,0,;8.2,2.1,20,0,;7.6,4,30,0,;6.5,6.6,35,0,;5.9,7.5,35.75,0,;4.9,8.8,34.98,0,|11.7,0,0,0,;11.1,2.2,20,0,;10.4,4.1,30,0,;9.4,5.9,35,0,;8.3,7.8,37.87,0,;6.6,10.3,35,0,|15.3,0,0,0,;14.8,2.3,20,0,;13.9,4.3,30,0,;13,5.7,35,0,;10.8,9,38.95,0,;8.6,11.8,35,0,|19.2,0,0,0,;18.6,2.3,20,0,;17.7,4.4,30,0,;16.9,5.7,35,0,;15.4,8,40,0,;13.7,10.1,41.25,0,;12.1,12,40,0,;10.9,13.2,35.65,0,|23.7,0,0,0,;23.1,2.4,20,0,;22.1,4.5,30,0,;21.5,5.6,35,0,;19.9,7.9,40,0,;17,11.3,41.58,0,;14,14.3,39.97,0,|28.8,0,0,0,;28,2.5,20,0,;26.9,4.6,30,0,;24.7,7.9,40,0,;20.6,12.4,42.55,0,;16.7,16.2,40,0,|34.4,0,0,0,;33.6,2.6,20,0,;32.4,4.7,30,0,;31.7,5.8,35,0,;29.9,7.9,40,0,;24.5,13.5,43.87,0,;19.8,17.8,39.97,0,|40.4,0,0,0,;39.4,2.7,20,0,;38.2,4.8,30,0,;37.4,6,35,0,;35.6,8.1,40,0,;28.9,14.7,43.95,0,;23.2,19.3,40,0,|46.8,0,0,0,;45.7,2.8,20,0,;44.6,4.85,30,0,;43.5,6.25,35,0,;41.3,8.55,40,0,;33.3,15.65,44.5,0,;27,20.7,40,0,</v>
       </c>
     </row>
-    <row r="144" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="144" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C144" t="str">
+        <f>PumpOG!B133</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D144" t="str">
+        <f>PumpOG!B133</f>
+        <v>SPSA</v>
+      </c>
       <c r="E144" t="str">
         <f>PumpOG!A133</f>
         <v>VS40P-RUBBER</v>
@@ -14368,7 +15420,15 @@
         <v>40.6,0,0,0,;39.3,2.9,20,0,;37.5,5.2,30,0,;35.8,6.8,35,0,;32.2,9.6,40,0,;30,11.1,40.5,0,;28,12.3,40,0,;22.2,15.6,35,0,</v>
       </c>
     </row>
-    <row r="145" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="145" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C145" t="str">
+        <f>PumpOG!B134</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D145" t="str">
+        <f>PumpOG!B134</f>
+        <v>SPSA</v>
+      </c>
       <c r="E145" t="str">
         <f>PumpOG!A134</f>
         <v>VS65Q-METAL</v>
@@ -14382,7 +15442,15 @@
         <v>48.8,0,0,0,;48.5,7.1,25,0,;47.35,12.3,35,0,;46.65,14.1,40,0,;45,17.9,45,0,;43.5,21.2,48,0,;41.8,24.4,50,0,;39,29.3,51,0,;35.5,35,50,0,;32.5,40.1,48,0,</v>
       </c>
     </row>
-    <row r="146" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="146" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C146" t="str">
+        <f>PumpOG!B135</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D146" t="str">
+        <f>PumpOG!B135</f>
+        <v>SPSA</v>
+      </c>
       <c r="E146" t="str">
         <f>PumpOG!A135</f>
         <v>VS65Q-RUBBER</v>
@@ -14396,7 +15464,15 @@
         <v>6.9,0,0,0,;6.9,2.1,20,0,;6.7,4,30,0,;6.6,6,40,0,;6.4,7.7,45,0,;5.6,11.5,46,0,;4.4,15.3,45,0,|11.7,0,0,0,;11.6,2.7,20,0,;11.5,4.9,30,0,;11,7.7,40,0,;10.6,10,45,0,;9.4,14.6,47,0,;7.6,19.5,45,0,|17.6,0,0,0,;17.5,3.2,20,0,;17.1,5.9,30,0,;16.6,9.4,40,0,;16,12.2,45,0,;14.6,17,50,0,;14.3,18.1,50.1,0,;13.7,19.1,50,0,;11.4,24.2,45,0,|24.5,0,0,0,;24.3,4,20,0,;24,7,30,0,;23.2,11.2,40,0,;22.5,14.2,45,0,;21,18.7,50,0,;19.8,21.5,50.2,0,;18.8,23.4,50,0,;15.6,28.7,45,0,|32.6,0,0,0,;32.3,4.8,20,0,;31.8,8.2,30,0,;30.9,12.7,40,0,;30.1,16,45,0,;28.2,21,50,0,;26.3,24.9,50.3,0,;24.9,27.1,50,0,;20.6,33,45,0,|41.9,0,0,0,;41.6,5.6,20,0,;41.1,9.5,30,0,;40.1,14.3,40,0,;38.8,17.9,45,0,;36.5,23.7,50,0,;34,28,50.4,0,;32.1,30.8,50,0,;26.6,37.4,45,0,|49.8,0,0,0,;49.4,6.2,20,0,;48.8,10.5,30,0,;47.5,15.4,40,0,;46,19.5,45,0,;43,26,50,0,;40.6,30.1,50.5,0,;38,33.7,50,0,;31.7,40.5,45,0,</v>
       </c>
     </row>
-    <row r="147" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C147" t="str">
+        <f>PumpOG!B136</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D147" t="str">
+        <f>PumpOG!B136</f>
+        <v>SPSA</v>
+      </c>
       <c r="E147" t="str">
         <f>PumpOG!A136</f>
         <v>VT100R-METAL</v>
@@ -14410,7 +15486,15 @@
         <v>29.1,0,0,0,;28.9,7,20,0,;28.7,12.1,30,0,;28.3,19.2,40,0,;27.5,28,50,0,;26.6,36,55,0,;23.8,51.8,58,0,;21.5,61.6,55,0,</v>
       </c>
     </row>
-    <row r="148" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="148" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C148" t="str">
+        <f>PumpOG!B137</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D148" t="str">
+        <f>PumpOG!B137</f>
+        <v>SPSA</v>
+      </c>
       <c r="E148" t="str">
         <f>PumpOG!A137</f>
         <v>VT150R-METAL</v>
@@ -14424,7 +15508,15 @@
         <v>25.2,0,0,0,;25.3,20.2,20,0,;25.1,32.1,30,0,;24.7,48.4,40,0,;24.1,59.5,45,0,;23.4,71.6,50,0,;21.8,92.1,55,0,;20,109.9,56,0,;18.4,122.7,55,0,</v>
       </c>
     </row>
-    <row r="149" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="149" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C149" t="str">
+        <f>PumpOG!B138</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D149" t="str">
+        <f>PumpOG!B138</f>
+        <v>SPSA</v>
+      </c>
       <c r="E149" t="str">
         <f>PumpOG!A138</f>
         <v>VT200S-METAL</v>
@@ -14438,7 +15530,15 @@
         <v>26.6,0,0,0,;25.9,40.1,30,0,;25.2,64.6,40,0,;23.9,102.3,50,0,;22.1,148.9,55,0,;20.8,176.7,55.7,0,;19.2,205.4,55,0,</v>
       </c>
     </row>
-    <row r="150" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="150" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C150" t="str">
+        <f>PumpOG!B139</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D150" t="str">
+        <f>PumpOG!B139</f>
+        <v>SPSA</v>
+      </c>
       <c r="E150" t="str">
         <f>PumpOG!A139</f>
         <v>VT50Q-METAL</v>
@@ -14452,7 +15552,15 @@
         <v>30.2,0,0,0,;30,2.6,20,0,;29.6,4.5,30,0,;28.4,7.3,40,0,;27,9.5,45,0,;25,12,47,0,;22.7,14.2,45,0,</v>
       </c>
     </row>
-    <row r="151" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="151" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C151" t="str">
+        <f>PumpOG!B140</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D151" t="str">
+        <f>PumpOG!B140</f>
+        <v>SPSA</v>
+      </c>
       <c r="E151" t="str">
         <f>PumpOG!A140</f>
         <v>VT80Q-METAL</v>
@@ -14466,7 +15574,15 @@
         <v>29.4,0,0,0,;28.9,6.5,20,0,;28.5,10.4,30,0,;27.9,15,40,0,;26.8,22.2,50,0,;25.6,28.7,55,0,;23.9,36.2,57,0,;22.5,41,54.98,0,</v>
       </c>
     </row>
-    <row r="152" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="152" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C152" t="str">
+        <f>PumpOG!B141</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D152" t="str">
+        <f>PumpOG!B141</f>
+        <v>SPSA</v>
+      </c>
       <c r="E152" t="str">
         <f>PumpOG!A141</f>
         <v>WHP100-400PE</v>
@@ -14480,7 +15596,15 @@
         <v>132.5,0,0,4.7,;131.2,22.5,40,4.7,;129.2,32,50,5.5,;123.5,46.5,60,5.9,;115,61.7,65,6.5,;104,77.7,67,7.9,;90.3,94.7,65,9.4,;76,110.8,60,10.6,</v>
       </c>
     </row>
-    <row r="153" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="153" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C153" t="str">
+        <f>PumpOG!B142</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D153" t="str">
+        <f>PumpOG!B142</f>
+        <v>SPSA</v>
+      </c>
       <c r="E153" t="str">
         <f>PumpOG!A142</f>
         <v>WHP100-500PE</v>
@@ -14494,7 +15618,15 @@
         <v>132.5,0,0,4.7,;131.2,22.5,40,4.7,;129.2,34,50,5.5,;123.5,46.5,60,5.9,;115,61.7,65,6.5,;104,77.7,67,7.9,;90.3,94.7,65,9.4,;76,110.8,60,10.6,</v>
       </c>
     </row>
-    <row r="154" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="154" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C154" t="str">
+        <f>PumpOG!B143</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D154" t="str">
+        <f>PumpOG!B143</f>
+        <v>SPSA</v>
+      </c>
       <c r="E154" t="str">
         <f>PumpOG!A143</f>
         <v>WHP125-330P</v>
@@ -14508,7 +15640,15 @@
         <v>142.7,0,0,3.2,;148.4,17.5,35,4,;150,32.8,50,4.5,;149.4,41.1,57,5.4,;148.1,48.9,62,5.9,;145.7,56.9,66,6.5,;142.7,66.1,69,7.2,;139,73.2,70.5,7.8,;131.1,85.3,71.5,8.5,;120.8,98.5,70.5,9,;114.1,105.6,69,9.5,;104.3,114.6,66,10,;100.7,117.9,64,10.4,</v>
       </c>
     </row>
-    <row r="155" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="155" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C155" t="str">
+        <f>PumpOG!B144</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D155" t="str">
+        <f>PumpOG!B144</f>
+        <v>SPSA</v>
+      </c>
       <c r="E155" t="str">
         <f>PumpOG!A144</f>
         <v>WHP150-400PE</v>
@@ -14522,7 +15662,15 @@
         <v>80,0,0,2.9,;79.1,29,40,2.9,;77.9,42.9,50,3,;75.7,61.6,60,3.4,;71.1,89.8,70,4.5,;68.3,102.6,73,5.2,;60.3,133.4,76,7.6,;50.6,163.1,73,10.6,</v>
       </c>
     </row>
-    <row r="156" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="156" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C156" t="str">
+        <f>PumpOG!B145</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D156" t="str">
+        <f>PumpOG!B145</f>
+        <v>SPSA</v>
+      </c>
       <c r="E156" t="str">
         <f>PumpOG!A145</f>
         <v>WHP150-440Q</v>
@@ -14536,7 +15684,15 @@
         <v>28.4,0,0,0,;30.1,15.2,30,0,;30.3,26.9,50,0,;30.3,36.7,60,0,;30.1,48.4,68,0,;29.2,58.7,72,0,;28.4,67,74,0,;27,75.8,74.7,0,;25.7,83.7,74,0,;23.7,92.5,72,0,;21.2,102.3,69,0,|74.2,0,0,0,;77.2,22.5,30,0,;78.6,42.1,50,0,;78.6,56.8,60,0,;77.8,74.9,68,0,;76.4,89,72,0,;74.8,99.8,74,0,;72.6,110.1,75,0,;70.3,120.8,75.7,0,;67.3,130.6,75,0,;64.3,140.4,74,0,;60.1,152.6,72,0,;54.1,167.3,69,0,|141.2,0,0,3,;146.8,32.8,35,4,;148.7,57.2,50,4.7,;149,77.8,60,4.9,;147.3,101.8,68,6.8,;144.8,120.4,72,7.4,;142.1,134.5,74,7.6,;139.3,145.8,75,7.7,;133.5,165.4,75.7,9.8,;125.2,186.4,75,9.7,;120.3,197.2,74,10.9,;112.8,212.3,72,11.4,;104,228,69,12,</v>
       </c>
     </row>
-    <row r="157" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="157" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C157" t="str">
+        <f>PumpOG!B146</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D157" t="str">
+        <f>PumpOG!B146</f>
+        <v>SPSA</v>
+      </c>
       <c r="E157" t="str">
         <f>PumpOG!A146</f>
         <v>WHP150-500PF</v>
@@ -14550,7 +15706,15 @@
         <v>132.5,0,0,3.9,;131,47,50,3.9,;128.2,70.5,60,4.3,;124.9,85.5,65,4.7,;118.1,109.5,70,5.6,;104,150,73,7.6,;82.5,194,70,11,</v>
       </c>
     </row>
-    <row r="158" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="158" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C158" t="str">
+        <f>PumpOG!B147</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D158" t="str">
+        <f>PumpOG!B147</f>
+        <v>SPSA</v>
+      </c>
       <c r="E158" t="str">
         <f>PumpOG!A147</f>
         <v>WHP200-500PF</v>
@@ -14564,7 +15728,15 @@
         <v>79.4,0,0,3.4,;80.2,64.1,50,3.4,;79.4,85.9,60,3.6,;76.9,124.6,70,4.1,;73.6,157.3,75,4.7,;71.3,176.6,77,5.3,;61.3,237.7,79,7.7,;50.4,290.9,77,10.5,</v>
       </c>
     </row>
-    <row r="159" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="159" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C159" t="str">
+        <f>PumpOG!B148</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D159" t="str">
+        <f>PumpOG!B148</f>
+        <v>SPSA</v>
+      </c>
       <c r="E159" t="str">
         <f>PumpOG!A148</f>
         <v>WHP200-550R</v>
@@ -14578,7 +15750,15 @@
         <v>16.7,0,0,0,;17.2,20.4,40,0,;17.5,36.9,50,0,;17.2,51,60,0,;17,69.8,68,0,;15.5,97.3,70,0,;12.8,126.3,68,0,|83.6,0,0,0,;87.4,43.9,40,0,;88,69,50,0,;88.3,93.3,60,0,;87.4,120,68,0,;86.2,145.1,73,0,;84.2,167.8,76,0,;80.9,195.3,78,0,;76.7,222,78.6,0,;72.3,248.6,78,0,;66.3,276.9,76,0,;60.7,302,73,0,|144.2,0,0,2.9,;149.3,52.5,40,3.9,;150.8,87.1,50,4.7,;151.1,117.6,60,5.4,;150.2,153.7,68,6.1,;148.1,185.9,73,6.8,;144.5,216.5,76,7.6,;139.5,254.1,78,8.4,;132,293.3,78.6,9,;123.4,331.8,78,9.5,;112.4,372.5,76,10,;103.2,400,72,10.5,</v>
       </c>
     </row>
-    <row r="160" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="160" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C160" t="str">
+        <f>PumpOG!B149</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D160" t="str">
+        <f>PumpOG!B149</f>
+        <v>SPSA</v>
+      </c>
       <c r="E160" t="str">
         <f>PumpOG!A149</f>
         <v>26/22-MD550G-M</v>
@@ -14592,7 +15772,15 @@
         <v>14.4,0,0,2.1,;14.5,377.2,60,2.3,;14.3,515,70,2.5,;14,664.7,78,2.5,;13.5,754.5,81,2.6,;12.9,880.2,84,2.9,;11.7,1096,86,3.2,;10.6,1281,84,3,;9.8,1401,80.9,3.3,|36.7,0,0,0,;37.1,616.8,60,0,;36.4,826.3,70,0,;35.2,1072,78,0,;34.4,1210,81,0,;33,1407,84,0,;30,1743,86,0,;27,2054,84,11.6,;25.2,2234,80.9,11.9,|51.8,0,0,8,;51.9,730.5,60,8.6,;51.2,982,70,9,;49.4,1270,78,9.5,;48.5,1443,81,10.1,;46.2,1677,84,10.5,;42.2,2066,86,11.4,;37.9,2437,84,12,;35.5,2653,80.9,12,</v>
       </c>
     </row>
-    <row r="161" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C161" t="str">
+        <f>PumpOG!B150</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D161" t="str">
+        <f>PumpOG!B150</f>
+        <v>SPSA</v>
+      </c>
       <c r="E161" t="str">
         <f>PumpOG!A150</f>
         <v>26/22-MD550G-R</v>
@@ -14606,7 +15794,15 @@
         <v>14.6,0,0,2.1,;15,267.5,50,2.4,;15,345.3,60,2.6,;14.9,462.1,70,2.6,;14.8,544.7,75,2.7,;14.6,651.8,80,2.7,;13.9,822,85,2.9,;12.4,1119,88,3.3,;10.6,1362,84.9,3.7,|28.6,0,0,0,;29.3,374.5,50,0,;29.4,491.2,60,0,;29.1,656.6,70,0,;29,758.8,75,0,;28.4,909.5,80,0,;27.1,1143,85,0,;24.2,1561,88,0,;20.7,1912,84.8,0,|41.8,0,0,6.3,;43.2,452.3,50,6.7,;43,598.2,60,7.2,;42.9,797.7,70,7.4,;42.3,929,75,7.5,;41.7,1109,80,7.7,;40,1396,85,8.2,;35.6,1897,88,9.5,;30.6,2325,84.8,10.6,</v>
       </c>
     </row>
-    <row r="162" spans="5:77" x14ac:dyDescent="0.3">
+    <row r="162" spans="3:77" x14ac:dyDescent="0.3">
+      <c r="C162" t="str">
+        <f>PumpOG!B151</f>
+        <v>SPSA</v>
+      </c>
+      <c r="D162" t="str">
+        <f>PumpOG!B151</f>
+        <v>SPSA</v>
+      </c>
       <c r="E162" t="str">
         <f>PumpOG!A151</f>
         <v>26/22-MD550TU-M</v>
@@ -14638,6 +15834,7 @@
     <col min="85" max="85" width="29.44140625" customWidth="1"/>
     <col min="86" max="86" width="15.5546875" customWidth="1"/>
     <col min="87" max="88" width="25.77734375" customWidth="1"/>
+    <col min="264" max="264" width="48.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:273" s="3" customFormat="1" x14ac:dyDescent="0.3">
